--- a/task2/恒瑞医药.xlsx
+++ b/task2/恒瑞医药.xlsx
@@ -518,10 +518,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>7926</v>
+      </c>
+      <c r="K2" t="n">
         <v>434450</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2385673562.5</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -558,10 +558,10 @@
         <v>0.74708454810495</v>
       </c>
       <c r="J3" t="n">
+        <v>6694</v>
+      </c>
+      <c r="K3" t="n">
         <v>368593</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2032606098.5</v>
       </c>
       <c r="L3" t="n">
         <v>0.007470845481049482</v>
@@ -600,10 +600,10 @@
         <v>-2.550189907759083</v>
       </c>
       <c r="J4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="K4" t="n">
         <v>495273</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2694656574.75</v>
       </c>
       <c r="L4" t="n">
         <v>-0.02550189907759082</v>
@@ -642,10 +642,10 @@
         <v>-0.1484780994803367</v>
       </c>
       <c r="J5" t="n">
+        <v>6398</v>
+      </c>
+      <c r="K5" t="n">
         <v>344534</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1854109721</v>
       </c>
       <c r="L5" t="n">
         <v>-0.001484780994803314</v>
@@ -684,10 +684,10 @@
         <v>1.040892193308554</v>
       </c>
       <c r="J6" t="n">
+        <v>12125</v>
+      </c>
+      <c r="K6" t="n">
         <v>656906</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3578988114.5</v>
       </c>
       <c r="L6" t="n">
         <v>0.01040892193308562</v>
@@ -726,10 +726,10 @@
         <v>1.416482707873442</v>
       </c>
       <c r="J7" t="n">
+        <v>8780</v>
+      </c>
+      <c r="K7" t="n">
         <v>480735</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2640316803.75</v>
       </c>
       <c r="L7" t="n">
         <v>0.01416482707873445</v>
@@ -768,10 +768,10 @@
         <v>-0.7618356611645233</v>
       </c>
       <c r="J8" t="n">
+        <v>6886</v>
+      </c>
+      <c r="K8" t="n">
         <v>377736</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2078209038</v>
       </c>
       <c r="L8" t="n">
         <v>-0.007618356611645227</v>
@@ -810,10 +810,10 @@
         <v>2.028879546700785</v>
       </c>
       <c r="J9" t="n">
+        <v>8949</v>
+      </c>
+      <c r="K9" t="n">
         <v>493188</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2717712474</v>
       </c>
       <c r="L9" t="n">
         <v>0.0202887954670079</v>
@@ -852,10 +852,10 @@
         <v>-3.457542099605875</v>
       </c>
       <c r="J10" t="n">
+        <v>12050</v>
+      </c>
+      <c r="K10" t="n">
         <v>660238</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3618104240</v>
       </c>
       <c r="L10" t="n">
         <v>-0.0345754209960587</v>
@@ -894,10 +894,10 @@
         <v>-0.2412321395435193</v>
       </c>
       <c r="J11" t="n">
+        <v>7320</v>
+      </c>
+      <c r="K11" t="n">
         <v>392241</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2101921458.75</v>
       </c>
       <c r="L11" t="n">
         <v>-0.002412321395435235</v>
@@ -936,10 +936,10 @@
         <v>-3.571428571428561</v>
       </c>
       <c r="J12" t="n">
+        <v>13136</v>
+      </c>
+      <c r="K12" t="n">
         <v>695180</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3678371175</v>
       </c>
       <c r="L12" t="n">
         <v>-0.03571428571428559</v>
@@ -978,10 +978,10 @@
         <v>-0.05787037037037256</v>
       </c>
       <c r="J13" t="n">
+        <v>6455</v>
+      </c>
+      <c r="K13" t="n">
         <v>334095</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1729442767.5</v>
       </c>
       <c r="L13" t="n">
         <v>-0.0005787037037037202</v>
@@ -1020,10 +1020,10 @@
         <v>-0.4439297432928083</v>
       </c>
       <c r="J14" t="n">
+        <v>7217</v>
+      </c>
+      <c r="K14" t="n">
         <v>373167</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1932258726</v>
       </c>
       <c r="L14" t="n">
         <v>-0.004439297432928035</v>
@@ -1062,10 +1062,10 @@
         <v>0.3489724699495924</v>
       </c>
       <c r="J15" t="n">
+        <v>4649</v>
+      </c>
+      <c r="K15" t="n">
         <v>240608</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1247973544</v>
       </c>
       <c r="L15" t="n">
         <v>0.003489724699495822</v>
@@ -1104,10 +1104,10 @@
         <v>0.3863987635239622</v>
       </c>
       <c r="J16" t="n">
+        <v>6046</v>
+      </c>
+      <c r="K16" t="n">
         <v>313281</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1621385815.5</v>
       </c>
       <c r="L16" t="n">
         <v>0.003863987635239541</v>
@@ -1146,10 +1146,10 @@
         <v>0.3656658968437215</v>
       </c>
       <c r="J17" t="n">
+        <v>8654</v>
+      </c>
+      <c r="K17" t="n">
         <v>451035</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2350681661.25</v>
       </c>
       <c r="L17" t="n">
         <v>0.003656658968437254</v>
@@ -1188,10 +1188,10 @@
         <v>1.534036433365301</v>
       </c>
       <c r="J18" t="n">
+        <v>10209</v>
+      </c>
+      <c r="K18" t="n">
         <v>536482</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2809019752</v>
       </c>
       <c r="L18" t="n">
         <v>0.01534036433365293</v>
@@ -1230,10 +1230,10 @@
         <v>-1.643059490084994</v>
       </c>
       <c r="J19" t="n">
+        <v>7495</v>
+      </c>
+      <c r="K19" t="n">
         <v>392269</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2054803089.25</v>
       </c>
       <c r="L19" t="n">
         <v>-0.01643059490084997</v>
@@ -1272,10 +1272,10 @@
         <v>-0.2496159754224183</v>
       </c>
       <c r="J20" t="n">
+        <v>5541</v>
+      </c>
+      <c r="K20" t="n">
         <v>287765</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1493500350</v>
       </c>
       <c r="L20" t="n">
         <v>-0.002496159754224236</v>
@@ -1314,10 +1314,10 @@
         <v>-0.09624639076035468</v>
       </c>
       <c r="J21" t="n">
+        <v>8580</v>
+      </c>
+      <c r="K21" t="n">
         <v>445355</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2304600786.25</v>
       </c>
       <c r="L21" t="n">
         <v>-0.0009624639076035724</v>
@@ -1356,10 +1356,10 @@
         <v>1.078998073217731</v>
       </c>
       <c r="J22" t="n">
+        <v>7623</v>
+      </c>
+      <c r="K22" t="n">
         <v>397725</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2077019381.25</v>
       </c>
       <c r="L22" t="n">
         <v>0.01078998073217741</v>
@@ -1398,10 +1398,10 @@
         <v>-0.4003049942813589</v>
       </c>
       <c r="J23" t="n">
+        <v>6225</v>
+      </c>
+      <c r="K23" t="n">
         <v>325712</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1711535132</v>
       </c>
       <c r="L23" t="n">
         <v>-0.004003049942813641</v>
@@ -1440,10 +1440,10 @@
         <v>0.4210526315789452</v>
       </c>
       <c r="J24" t="n">
+        <v>5608</v>
+      </c>
+      <c r="K24" t="n">
         <v>293678</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1535348584</v>
       </c>
       <c r="L24" t="n">
         <v>0.004210526315789442</v>
@@ -1482,10 +1482,10 @@
         <v>1.50562226033924</v>
       </c>
       <c r="J25" t="n">
+        <v>9028</v>
+      </c>
+      <c r="K25" t="n">
         <v>477923</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2536098399.5</v>
       </c>
       <c r="L25" t="n">
         <v>0.01505622260339234</v>
@@ -1524,10 +1524,10 @@
         <v>-1.14532482162974</v>
       </c>
       <c r="J26" t="n">
+        <v>5402</v>
+      </c>
+      <c r="K26" t="n">
         <v>286388</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1519145146</v>
       </c>
       <c r="L26" t="n">
         <v>-0.01145324821629745</v>
@@ -1566,10 +1566,10 @@
         <v>1.424501424501424</v>
       </c>
       <c r="J27" t="n">
+        <v>6773</v>
+      </c>
+      <c r="K27" t="n">
         <v>359263</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1906608741</v>
       </c>
       <c r="L27" t="n">
         <v>0.01424501424501434</v>
@@ -1608,10 +1608,10 @@
         <v>7.097378277153557</v>
       </c>
       <c r="J28" t="n">
+        <v>20946</v>
+      </c>
+      <c r="K28" t="n">
         <v>1158212</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6415046715</v>
       </c>
       <c r="L28" t="n">
         <v>0.07097378277153554</v>
@@ -1650,10 +1650,10 @@
         <v>0.7169085504458886</v>
       </c>
       <c r="J29" t="n">
+        <v>15754</v>
+      </c>
+      <c r="K29" t="n">
         <v>903716</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5187781698</v>
       </c>
       <c r="L29" t="n">
         <v>0.007169085504458828</v>
@@ -1692,10 +1692,10 @@
         <v>-1.215277777777783</v>
       </c>
       <c r="J30" t="n">
+        <v>11514</v>
+      </c>
+      <c r="K30" t="n">
         <v>658632</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3777419178</v>
       </c>
       <c r="L30" t="n">
         <v>-0.01215277777777779</v>
@@ -1734,10 +1734,10 @@
         <v>0.5448154657293538</v>
       </c>
       <c r="J31" t="n">
+        <v>8314</v>
+      </c>
+      <c r="K31" t="n">
         <v>473758</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2707171651.5</v>
       </c>
       <c r="L31" t="n">
         <v>0.005448154657293536</v>
@@ -1776,10 +1776,10 @@
         <v>0.01747946163257824</v>
       </c>
       <c r="J32" t="n">
+        <v>7634</v>
+      </c>
+      <c r="K32" t="n">
         <v>436928</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2496169664</v>
       </c>
       <c r="L32" t="n">
         <v>0.0001747946163257463</v>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>6933</v>
+      </c>
+      <c r="K33" t="n">
         <v>398191</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2297661617.75</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1860,10 +1860,10 @@
         <v>0.8912967493883224</v>
       </c>
       <c r="J34" t="n">
+        <v>7749</v>
+      </c>
+      <c r="K34" t="n">
         <v>444146</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2546844200.5</v>
       </c>
       <c r="L34" t="n">
         <v>0.008912967493883261</v>
@@ -1902,10 +1902,10 @@
         <v>1.784167677117619</v>
       </c>
       <c r="J35" t="n">
+        <v>11302</v>
+      </c>
+      <c r="K35" t="n">
         <v>660986</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3878831094.5</v>
       </c>
       <c r="L35" t="n">
         <v>0.01784167677117621</v>
@@ -1944,10 +1944,10 @@
         <v>-1.293396868618104</v>
       </c>
       <c r="J36" t="n">
+        <v>8746</v>
+      </c>
+      <c r="K36" t="n">
         <v>509442</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2967244929</v>
       </c>
       <c r="L36" t="n">
         <v>-0.01293396868618102</v>
@@ -1986,10 +1986,10 @@
         <v>-1.017241379310351</v>
       </c>
       <c r="J37" t="n">
+        <v>8241</v>
+      </c>
+      <c r="K37" t="n">
         <v>475570</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2751885805</v>
       </c>
       <c r="L37" t="n">
         <v>-0.01017241379310352</v>
@@ -2028,10 +2028,10 @@
         <v>-0.487719909423435</v>
       </c>
       <c r="J38" t="n">
+        <v>7440</v>
+      </c>
+      <c r="K38" t="n">
         <v>425295</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2437790940</v>
       </c>
       <c r="L38" t="n">
         <v>-0.004877199094234341</v>
@@ -2070,10 +2070,10 @@
         <v>0.6476457202870601</v>
       </c>
       <c r="J39" t="n">
+        <v>8106</v>
+      </c>
+      <c r="K39" t="n">
         <v>465834</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2677031539.5</v>
       </c>
       <c r="L39" t="n">
         <v>0.0064764572028706</v>
@@ -2112,10 +2112,10 @@
         <v>-1.913043478260872</v>
       </c>
       <c r="J40" t="n">
+        <v>8874</v>
+      </c>
+      <c r="K40" t="n">
         <v>505394</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2878218830</v>
       </c>
       <c r="L40" t="n">
         <v>-0.01913043478260867</v>
@@ -2154,10 +2154,10 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
+        <v>26692</v>
+      </c>
+      <c r="K41" t="n">
         <v>1630096</v>
-      </c>
-      <c r="K41" t="n">
-        <v>9937065216</v>
       </c>
       <c r="L41" t="n">
         <v>0.1000000000000001</v>
@@ -2196,10 +2196,10 @@
         <v>2.83687943262411</v>
       </c>
       <c r="J42" t="n">
+        <v>26542</v>
+      </c>
+      <c r="K42" t="n">
         <v>1682769</v>
-      </c>
-      <c r="K42" t="n">
-        <v>10700728071</v>
       </c>
       <c r="L42" t="n">
         <v>0.02836879432624118</v>
@@ -2238,10 +2238,10 @@
         <v>-0.3291536050156642</v>
       </c>
       <c r="J43" t="n">
+        <v>15398</v>
+      </c>
+      <c r="K43" t="n">
         <v>980849</v>
-      </c>
-      <c r="K43" t="n">
-        <v>6247517705.5</v>
       </c>
       <c r="L43" t="n">
         <v>-0.00329153605015664</v>
@@ -2280,10 +2280,10 @@
         <v>-1.085076269853758</v>
       </c>
       <c r="J44" t="n">
+        <v>11750</v>
+      </c>
+      <c r="K44" t="n">
         <v>742039</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4694324223.75</v>
       </c>
       <c r="L44" t="n">
         <v>-0.01085076269853757</v>
@@ -2322,10 +2322,10 @@
         <v>-2.527821939586639</v>
       </c>
       <c r="J45" t="n">
+        <v>11836</v>
+      </c>
+      <c r="K45" t="n">
         <v>734655</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4563676860</v>
       </c>
       <c r="L45" t="n">
         <v>-0.02527821939586639</v>
@@ -2364,10 +2364,10 @@
         <v>1.12542815201435</v>
       </c>
       <c r="J46" t="n">
+        <v>11250</v>
+      </c>
+      <c r="K46" t="n">
         <v>689613</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4217845511.25</v>
       </c>
       <c r="L46" t="n">
         <v>0.01125428152014352</v>
@@ -2406,10 +2406,10 @@
         <v>0.4838709677419309</v>
       </c>
       <c r="J47" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K47" t="n">
         <v>541443</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3362767112.25</v>
       </c>
       <c r="L47" t="n">
         <v>0.004838709677419395</v>
@@ -2448,10 +2448,10 @@
         <v>-1.155698234349918</v>
       </c>
       <c r="J48" t="n">
+        <v>9251</v>
+      </c>
+      <c r="K48" t="n">
         <v>572479</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3545076207.5</v>
       </c>
       <c r="L48" t="n">
         <v>-0.01155698234349922</v>
@@ -2490,10 +2490,10 @@
         <v>-1.250405975966216</v>
       </c>
       <c r="J49" t="n">
+        <v>8271</v>
+      </c>
+      <c r="K49" t="n">
         <v>504764</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3089912826</v>
       </c>
       <c r="L49" t="n">
         <v>-0.01250405975966218</v>
@@ -2532,10 +2532,10 @@
         <v>0.2960039467192891</v>
       </c>
       <c r="J50" t="n">
+        <v>5966</v>
+      </c>
+      <c r="K50" t="n">
         <v>362971</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2203415455.5</v>
       </c>
       <c r="L50" t="n">
         <v>0.002960039467192921</v>
@@ -2574,10 +2574,10 @@
         <v>0.1311690441055883</v>
       </c>
       <c r="J51" t="n">
+        <v>6976</v>
+      </c>
+      <c r="K51" t="n">
         <v>425752</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2598790208</v>
       </c>
       <c r="L51" t="n">
         <v>0.001311690441055946</v>
@@ -2616,10 +2616,10 @@
         <v>-0.36024234485017</v>
       </c>
       <c r="J52" t="n">
+        <v>6415</v>
+      </c>
+      <c r="K52" t="n">
         <v>391835</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2389017995</v>
       </c>
       <c r="L52" t="n">
         <v>-0.003602423448501701</v>
@@ -2658,10 +2658,10 @@
         <v>2.8923582580115</v>
       </c>
       <c r="J53" t="n">
+        <v>13207</v>
+      </c>
+      <c r="K53" t="n">
         <v>815296</v>
-      </c>
-      <c r="K53" t="n">
-        <v>5051166368</v>
       </c>
       <c r="L53" t="n">
         <v>0.02892358258011507</v>
@@ -2700,10 +2700,10 @@
         <v>0.3354096789650229</v>
       </c>
       <c r="J54" t="n">
+        <v>9092</v>
+      </c>
+      <c r="K54" t="n">
         <v>571266</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3593691589.5</v>
       </c>
       <c r="L54" t="n">
         <v>0.003354096789650152</v>
@@ -2742,10 +2742,10 @@
         <v>0.9232728430436139</v>
       </c>
       <c r="J55" t="n">
+        <v>9758</v>
+      </c>
+      <c r="K55" t="n">
         <v>614933</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3885915360.25</v>
       </c>
       <c r="L55" t="n">
         <v>0.009232728430436099</v>
@@ -2784,10 +2784,10 @@
         <v>-0.5047318611987386</v>
       </c>
       <c r="J56" t="n">
+        <v>11525</v>
+      </c>
+      <c r="K56" t="n">
         <v>728858</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4614399998</v>
       </c>
       <c r="L56" t="n">
         <v>-0.005047318611987373</v>
@@ -2826,10 +2826,10 @@
         <v>-2.203551046290426</v>
       </c>
       <c r="J57" t="n">
+        <v>15952</v>
+      </c>
+      <c r="K57" t="n">
         <v>997700</v>
-      </c>
-      <c r="K57" t="n">
-        <v>6288503100</v>
       </c>
       <c r="L57" t="n">
         <v>-0.02203551046290431</v>
@@ -2868,10 +2868,10 @@
         <v>1.880369589884914</v>
       </c>
       <c r="J58" t="n">
+        <v>10448</v>
+      </c>
+      <c r="K58" t="n">
         <v>650424</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4042222554</v>
       </c>
       <c r="L58" t="n">
         <v>0.01880369589884912</v>
@@ -2910,10 +2910,10 @@
         <v>1.813842482100239</v>
       </c>
       <c r="J59" t="n">
+        <v>13419</v>
+      </c>
+      <c r="K59" t="n">
         <v>858629</v>
-      </c>
-      <c r="K59" t="n">
-        <v>5500592031.25</v>
       </c>
       <c r="L59" t="n">
         <v>0.01813842482100236</v>
@@ -2952,10 +2952,10 @@
         <v>1.547116736990158</v>
       </c>
       <c r="J60" t="n">
+        <v>9835</v>
+      </c>
+      <c r="K60" t="n">
         <v>637719</v>
-      </c>
-      <c r="K60" t="n">
-        <v>4124766492</v>
       </c>
       <c r="L60" t="n">
         <v>0.01547116736990151</v>
@@ -2994,10 +2994,10 @@
         <v>1.969836872883966</v>
       </c>
       <c r="J61" t="n">
+        <v>12942</v>
+      </c>
+      <c r="K61" t="n">
         <v>849234</v>
-      </c>
-      <c r="K61" t="n">
-        <v>5562695008.5</v>
       </c>
       <c r="L61" t="n">
         <v>0.01969836872883968</v>
@@ -3036,10 +3036,10 @@
         <v>-1.44883791125869</v>
       </c>
       <c r="J62" t="n">
+        <v>8747</v>
+      </c>
+      <c r="K62" t="n">
         <v>575129</v>
-      </c>
-      <c r="K62" t="n">
-        <v>3777159707.5</v>
       </c>
       <c r="L62" t="n">
         <v>-0.01448837911258694</v>
@@ -3078,10 +3078,10 @@
         <v>-3.445635528330781</v>
       </c>
       <c r="J63" t="n">
+        <v>13059</v>
+      </c>
+      <c r="K63" t="n">
         <v>836169</v>
-      </c>
-      <c r="K63" t="n">
-        <v>5368414022.25</v>
       </c>
       <c r="L63" t="n">
         <v>-0.03445635528330782</v>
@@ -3120,10 +3120,10 @@
         <v>-0.0317208564631182</v>
       </c>
       <c r="J64" t="n">
+        <v>11365</v>
+      </c>
+      <c r="K64" t="n">
         <v>715902</v>
-      </c>
-      <c r="K64" t="n">
-        <v>4485305005.5</v>
       </c>
       <c r="L64" t="n">
         <v>-0.0003172085646311329</v>
@@ -3162,10 +3162,10 @@
         <v>5.076947485324453</v>
       </c>
       <c r="J65" t="n">
+        <v>15831</v>
+      </c>
+      <c r="K65" t="n">
         <v>1023186</v>
-      </c>
-      <c r="K65" t="n">
-        <v>6629222094</v>
       </c>
       <c r="L65" t="n">
         <v>0.05076947485324457</v>
@@ -3204,10 +3204,10 @@
         <v>3.200966329457935</v>
       </c>
       <c r="J66" t="n">
+        <v>12945</v>
+      </c>
+      <c r="K66" t="n">
         <v>872181</v>
-      </c>
-      <c r="K66" t="n">
-        <v>5877409713.75</v>
       </c>
       <c r="L66" t="n">
         <v>0.03200966329457944</v>
@@ -3246,10 +3246,10 @@
         <v>0.7607900512070377</v>
       </c>
       <c r="J67" t="n">
+        <v>15641</v>
+      </c>
+      <c r="K67" t="n">
         <v>1084490</v>
-      </c>
-      <c r="K67" t="n">
-        <v>7516600190</v>
       </c>
       <c r="L67" t="n">
         <v>0.007607900512070387</v>
@@ -3288,10 +3288,10 @@
         <v>4.515754319732829</v>
       </c>
       <c r="J68" t="n">
+        <v>16044</v>
+      </c>
+      <c r="K68" t="n">
         <v>1129369</v>
-      </c>
-      <c r="K68" t="n">
-        <v>7990285675</v>
       </c>
       <c r="L68" t="n">
         <v>0.04515754319732834</v>
@@ -3330,10 +3330,10 @@
         <v>-4.62628507918866</v>
       </c>
       <c r="J69" t="n">
+        <v>15765</v>
+      </c>
+      <c r="K69" t="n">
         <v>1102894</v>
-      </c>
-      <c r="K69" t="n">
-        <v>7692685650</v>
       </c>
       <c r="L69" t="n">
         <v>-0.04626285079188663</v>
@@ -3372,10 +3372,10 @@
         <v>5.564457392571001</v>
       </c>
       <c r="J70" t="n">
+        <v>13239</v>
+      </c>
+      <c r="K70" t="n">
         <v>936479</v>
-      </c>
-      <c r="K70" t="n">
-        <v>6636124313.75</v>
       </c>
       <c r="L70" t="n">
         <v>0.05564457392571009</v>
@@ -3414,10 +3414,10 @@
         <v>-0.2207810128328917</v>
       </c>
       <c r="J71" t="n">
+        <v>10298</v>
+      </c>
+      <c r="K71" t="n">
         <v>748209</v>
-      </c>
-      <c r="K71" t="n">
-        <v>5439853534.5</v>
       </c>
       <c r="L71" t="n">
         <v>-0.002207810128328935</v>
@@ -3456,10 +3456,10 @@
         <v>-1.68718019637671</v>
       </c>
       <c r="J72" t="n">
+        <v>10717</v>
+      </c>
+      <c r="K72" t="n">
         <v>767670</v>
-      </c>
-      <c r="K72" t="n">
-        <v>5523001815</v>
       </c>
       <c r="L72" t="n">
         <v>-0.01687180196376714</v>
@@ -3498,10 +3498,10 @@
         <v>-1.083134055422718</v>
       </c>
       <c r="J73" t="n">
+        <v>6634</v>
+      </c>
+      <c r="K73" t="n">
         <v>468204</v>
-      </c>
-      <c r="K73" t="n">
-        <v>3312660351</v>
       </c>
       <c r="L73" t="n">
         <v>-0.01083134055422719</v>
@@ -3540,10 +3540,10 @@
         <v>-2.88680318543798</v>
       </c>
       <c r="J74" t="n">
+        <v>28803</v>
+      </c>
+      <c r="K74" t="n">
         <v>1942359</v>
-      </c>
-      <c r="K74" t="n">
-        <v>12981756376.5</v>
       </c>
       <c r="L74" t="n">
         <v>-0.02886803185437981</v>
@@ -3582,10 +3582,10 @@
         <v>1.054327134280274</v>
       </c>
       <c r="J75" t="n">
+        <v>12109</v>
+      </c>
+      <c r="K75" t="n">
         <v>831215</v>
-      </c>
-      <c r="K75" t="n">
-        <v>5707537797.5</v>
       </c>
       <c r="L75" t="n">
         <v>0.01054327134280264</v>
@@ -3624,10 +3624,10 @@
         <v>0.1304158817562515</v>
       </c>
       <c r="J76" t="n">
+        <v>8871</v>
+      </c>
+      <c r="K76" t="n">
         <v>611882</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4220456095</v>
       </c>
       <c r="L76" t="n">
         <v>0.001304158817562406</v>
@@ -3666,10 +3666,10 @@
         <v>0.07235890014473427</v>
       </c>
       <c r="J77" t="n">
+        <v>6287</v>
+      </c>
+      <c r="K77" t="n">
         <v>434582</v>
-      </c>
-      <c r="K77" t="n">
-        <v>2997855281.5</v>
       </c>
       <c r="L77" t="n">
         <v>0.0007235890014474222</v>
@@ -3708,10 +3708,10 @@
         <v>1.417208966015892</v>
       </c>
       <c r="J78" t="n">
+        <v>8406</v>
+      </c>
+      <c r="K78" t="n">
         <v>586034</v>
-      </c>
-      <c r="K78" t="n">
-        <v>4095352100.5</v>
       </c>
       <c r="L78" t="n">
         <v>0.01417208966015893</v>
@@ -3750,10 +3750,10 @@
         <v>1.368886353914171</v>
       </c>
       <c r="J79" t="n">
+        <v>12222</v>
+      </c>
+      <c r="K79" t="n">
         <v>865639</v>
-      </c>
-      <c r="K79" t="n">
-        <v>6160536353.25</v>
       </c>
       <c r="L79" t="n">
         <v>0.01368886353914167</v>
@@ -3792,10 +3792,10 @@
         <v>-2.025601350400897</v>
       </c>
       <c r="J80" t="n">
+        <v>7451</v>
+      </c>
+      <c r="K80" t="n">
         <v>524392</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3690146504</v>
       </c>
       <c r="L80" t="n">
         <v>-0.02025601350400896</v>
@@ -3834,10 +3834,10 @@
         <v>2.010050251256269</v>
       </c>
       <c r="J81" t="n">
+        <v>8147</v>
+      </c>
+      <c r="K81" t="n">
         <v>576542</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4102672872</v>
       </c>
       <c r="L81" t="n">
         <v>0.02010050251256268</v>
@@ -3876,10 +3876,10 @@
         <v>-1.900070372976769</v>
       </c>
       <c r="J82" t="n">
+        <v>7979</v>
+      </c>
+      <c r="K82" t="n">
         <v>561330</v>
-      </c>
-      <c r="K82" t="n">
-        <v>3934782967.5</v>
       </c>
       <c r="L82" t="n">
         <v>-0.0190007037297677</v>
@@ -3918,10 +3918,10 @@
         <v>0.5882352941176421</v>
       </c>
       <c r="J83" t="n">
+        <v>5655</v>
+      </c>
+      <c r="K83" t="n">
         <v>395302</v>
-      </c>
-      <c r="K83" t="n">
-        <v>2762073899.5</v>
       </c>
       <c r="L83" t="n">
         <v>0.00588235294117645</v>
@@ -3960,10 +3960,10 @@
         <v>3.080872913992293</v>
       </c>
       <c r="J84" t="n">
+        <v>10217</v>
+      </c>
+      <c r="K84" t="n">
         <v>739039</v>
-      </c>
-      <c r="K84" t="n">
-        <v>5345099567.5</v>
       </c>
       <c r="L84" t="n">
         <v>0.03080872913992283</v>
@@ -4002,10 +4002,10 @@
         <v>-3.030303030303027</v>
       </c>
       <c r="J85" t="n">
+        <v>9924</v>
+      </c>
+      <c r="K85" t="n">
         <v>699045</v>
-      </c>
-      <c r="K85" t="n">
-        <v>4919179665</v>
       </c>
       <c r="L85" t="n">
         <v>-0.03030303030303028</v>
@@ -4044,10 +4044,10 @@
         <v>-1.255707762557071</v>
       </c>
       <c r="J86" t="n">
+        <v>9324</v>
+      </c>
+      <c r="K86" t="n">
         <v>647991</v>
-      </c>
-      <c r="K86" t="n">
-        <v>4479885778.5</v>
       </c>
       <c r="L86" t="n">
         <v>-0.01255707762557068</v>
@@ -4086,10 +4086,10 @@
         <v>3.395953757225425</v>
       </c>
       <c r="J87" t="n">
+        <v>8245</v>
+      </c>
+      <c r="K87" t="n">
         <v>579451</v>
-      </c>
-      <c r="K87" t="n">
-        <v>4069629235.75</v>
       </c>
       <c r="L87" t="n">
         <v>0.03395953757225434</v>
@@ -4128,10 +4128,10 @@
         <v>-0.5590496156533773</v>
       </c>
       <c r="J88" t="n">
+        <v>8308</v>
+      </c>
+      <c r="K88" t="n">
         <v>592793</v>
-      </c>
-      <c r="K88" t="n">
-        <v>4201123991</v>
       </c>
       <c r="L88" t="n">
         <v>-0.005590496156533731</v>
@@ -4170,10 +4170,10 @@
         <v>-4.146170063246666</v>
       </c>
       <c r="J89" t="n">
+        <v>10191</v>
+      </c>
+      <c r="K89" t="n">
         <v>706101</v>
-      </c>
-      <c r="K89" t="n">
-        <v>4895221707.75</v>
       </c>
       <c r="L89" t="n">
         <v>-0.04146170063246668</v>
@@ -4212,10 +4212,10 @@
         <v>-1.788856304985335</v>
       </c>
       <c r="J90" t="n">
+        <v>8006</v>
+      </c>
+      <c r="K90" t="n">
         <v>532287</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3549156644.25</v>
       </c>
       <c r="L90" t="n">
         <v>-0.01788856304985331</v>
@@ -4254,10 +4254,10 @@
         <v>-4.045983875783827</v>
       </c>
       <c r="J91" t="n">
+        <v>10660</v>
+      </c>
+      <c r="K91" t="n">
         <v>702947</v>
-      </c>
-      <c r="K91" t="n">
-        <v>4626094207</v>
       </c>
       <c r="L91" t="n">
         <v>-0.04045983875783832</v>
@@ -4296,10 +4296,10 @@
         <v>3.314143457289575</v>
       </c>
       <c r="J92" t="n">
+        <v>7829</v>
+      </c>
+      <c r="K92" t="n">
         <v>511232</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3331954560</v>
       </c>
       <c r="L92" t="n">
         <v>0.03314143457289576</v>
@@ -4338,10 +4338,10 @@
         <v>0.662650602409635</v>
       </c>
       <c r="J93" t="n">
+        <v>6909</v>
+      </c>
+      <c r="K93" t="n">
         <v>460378</v>
-      </c>
-      <c r="K93" t="n">
-        <v>3078662780.5</v>
       </c>
       <c r="L93" t="n">
         <v>0.006626506024096424</v>
@@ -4380,10 +4380,10 @@
         <v>-2.603231597845615</v>
       </c>
       <c r="J94" t="n">
+        <v>5298</v>
+      </c>
+      <c r="K94" t="n">
         <v>349507</v>
-      </c>
-      <c r="K94" t="n">
-        <v>2309804386.25</v>
       </c>
       <c r="L94" t="n">
         <v>-0.02603231597845612</v>
@@ -4422,10 +4422,10 @@
         <v>0.04608294930875751</v>
       </c>
       <c r="J95" t="n">
+        <v>4983</v>
+      </c>
+      <c r="K95" t="n">
         <v>326717</v>
-      </c>
-      <c r="K95" t="n">
-        <v>2143753595.5</v>
       </c>
       <c r="L95" t="n">
         <v>0.0004608294930876777</v>
@@ -4464,10 +4464,10 @@
         <v>1.335789958544457</v>
       </c>
       <c r="J96" t="n">
+        <v>5621</v>
+      </c>
+      <c r="K96" t="n">
         <v>369560</v>
-      </c>
-      <c r="K96" t="n">
-        <v>2431889580</v>
       </c>
       <c r="L96" t="n">
         <v>0.01335789958544464</v>
@@ -4506,10 +4506,10 @@
         <v>-1.121212121212114</v>
       </c>
       <c r="J97" t="n">
+        <v>6054</v>
+      </c>
+      <c r="K97" t="n">
         <v>398048</v>
-      </c>
-      <c r="K97" t="n">
-        <v>2620250472</v>
       </c>
       <c r="L97" t="n">
         <v>-0.01121212121212112</v>
@@ -4548,10 +4548,10 @@
         <v>-0.1838798651547725</v>
       </c>
       <c r="J98" t="n">
+        <v>5268</v>
+      </c>
+      <c r="K98" t="n">
         <v>342785</v>
-      </c>
-      <c r="K98" t="n">
-        <v>2224674650</v>
       </c>
       <c r="L98" t="n">
         <v>-0.00183879865154768</v>
@@ -4590,10 +4590,10 @@
         <v>0.5526558182376411</v>
       </c>
       <c r="J99" t="n">
+        <v>5701</v>
+      </c>
+      <c r="K99" t="n">
         <v>372753</v>
-      </c>
-      <c r="K99" t="n">
-        <v>2442743597.25</v>
       </c>
       <c r="L99" t="n">
         <v>0.005526558182376462</v>
@@ -4632,10 +4632,10 @@
         <v>2.30534351145039</v>
       </c>
       <c r="J100" t="n">
+        <v>7621</v>
+      </c>
+      <c r="K100" t="n">
         <v>508925</v>
-      </c>
-      <c r="K100" t="n">
-        <v>3408779650</v>
       </c>
       <c r="L100" t="n">
         <v>0.02305343511450397</v>
@@ -4674,10 +4674,10 @@
         <v>-5.058946425906592</v>
       </c>
       <c r="J101" t="n">
+        <v>16797</v>
+      </c>
+      <c r="K101" t="n">
         <v>1082090</v>
-      </c>
-      <c r="K101" t="n">
-        <v>6974070050</v>
       </c>
       <c r="L101" t="n">
         <v>-0.05058946425906596</v>
@@ -4716,10 +4716,10 @@
         <v>0.6287331027978601</v>
       </c>
       <c r="J102" t="n">
+        <v>8810</v>
+      </c>
+      <c r="K102" t="n">
         <v>562175</v>
-      </c>
-      <c r="K102" t="n">
-        <v>3581195293.75</v>
       </c>
       <c r="L102" t="n">
         <v>0.006287331027978516</v>
@@ -4758,10 +4758,10 @@
         <v>-1.780693533270843</v>
       </c>
       <c r="J103" t="n">
+        <v>9594</v>
+      </c>
+      <c r="K103" t="n">
         <v>608740</v>
-      </c>
-      <c r="K103" t="n">
-        <v>3862303115</v>
       </c>
       <c r="L103" t="n">
         <v>-0.01780693533270838</v>
@@ -4800,10 +4800,10 @@
         <v>2.019720101781175</v>
       </c>
       <c r="J104" t="n">
+        <v>13129</v>
+      </c>
+      <c r="K104" t="n">
         <v>837064</v>
-      </c>
-      <c r="K104" t="n">
-        <v>5361394920</v>
       </c>
       <c r="L104" t="n">
         <v>0.02019720101781175</v>
@@ -4842,10 +4842,10 @@
         <v>-1.16913484021825</v>
       </c>
       <c r="J105" t="n">
+        <v>7172</v>
+      </c>
+      <c r="K105" t="n">
         <v>460306</v>
-      </c>
-      <c r="K105" t="n">
-        <v>2947914700.5</v>
       </c>
       <c r="L105" t="n">
         <v>-0.01169134840218244</v>
@@ -4884,10 +4884,10 @@
         <v>-2.334384858044159</v>
       </c>
       <c r="J106" t="n">
+        <v>8227</v>
+      </c>
+      <c r="K106" t="n">
         <v>515610</v>
-      </c>
-      <c r="K106" t="n">
-        <v>3226945185</v>
       </c>
       <c r="L106" t="n">
         <v>-0.02334384858044158</v>
@@ -4926,10 +4926,10 @@
         <v>0.06459948320413299</v>
       </c>
       <c r="J107" t="n">
+        <v>5426</v>
+      </c>
+      <c r="K107" t="n">
         <v>334381</v>
-      </c>
-      <c r="K107" t="n">
-        <v>2064551889.25</v>
       </c>
       <c r="L107" t="n">
         <v>0.0006459948320414188</v>
@@ -4968,10 +4968,10 @@
         <v>0.7424144609425449</v>
       </c>
       <c r="J108" t="n">
+        <v>4061</v>
+      </c>
+      <c r="K108" t="n">
         <v>252524</v>
-      </c>
-      <c r="K108" t="n">
-        <v>1567795254</v>
       </c>
       <c r="L108" t="n">
         <v>0.00742414460942542</v>
@@ -5010,10 +5010,10 @@
         <v>-1.34572252483179</v>
       </c>
       <c r="J109" t="n">
+        <v>4380</v>
+      </c>
+      <c r="K109" t="n">
         <v>270654</v>
-      </c>
-      <c r="K109" t="n">
-        <v>1675145269.5</v>
       </c>
       <c r="L109" t="n">
         <v>-0.01345722524831794</v>
@@ -5052,10 +5052,10 @@
         <v>0.4059759662227996</v>
       </c>
       <c r="J110" t="n">
+        <v>6422</v>
+      </c>
+      <c r="K110" t="n">
         <v>396248</v>
-      </c>
-      <c r="K110" t="n">
-        <v>2439797998</v>
       </c>
       <c r="L110" t="n">
         <v>0.004059759662228046</v>
@@ -5094,10 +5094,10 @@
         <v>-1.245350153647091</v>
       </c>
       <c r="J111" t="n">
+        <v>4474</v>
+      </c>
+      <c r="K111" t="n">
         <v>275160</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1693678590</v>
       </c>
       <c r="L111" t="n">
         <v>-0.01245350153647096</v>
@@ -5136,10 +5136,10 @@
         <v>1.703242712086471</v>
       </c>
       <c r="J112" t="n">
+        <v>8349</v>
+      </c>
+      <c r="K112" t="n">
         <v>514268</v>
-      </c>
-      <c r="K112" t="n">
-        <v>3177404838</v>
       </c>
       <c r="L112" t="n">
         <v>0.01703242712086461</v>
@@ -5178,10 +5178,10 @@
         <v>2.351046698872787</v>
       </c>
       <c r="J113" t="n">
+        <v>8053</v>
+      </c>
+      <c r="K113" t="n">
         <v>508318</v>
-      </c>
-      <c r="K113" t="n">
-        <v>3205834546.5</v>
       </c>
       <c r="L113" t="n">
         <v>0.02351046698872783</v>
@@ -5220,10 +5220,10 @@
         <v>-1.038388923851485</v>
       </c>
       <c r="J114" t="n">
+        <v>5057</v>
+      </c>
+      <c r="K114" t="n">
         <v>319504</v>
-      </c>
-      <c r="K114" t="n">
-        <v>2020942676</v>
       </c>
       <c r="L114" t="n">
         <v>-0.01038388923851485</v>
@@ -5262,10 +5262,10 @@
         <v>-1.748807631160575</v>
       </c>
       <c r="J115" t="n">
+        <v>5059</v>
+      </c>
+      <c r="K115" t="n">
         <v>315385</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1964454318.75</v>
       </c>
       <c r="L115" t="n">
         <v>-0.01748807631160576</v>
@@ -5304,10 +5304,10 @@
         <v>-0.03236245954691912</v>
       </c>
       <c r="J116" t="n">
+        <v>3551</v>
+      </c>
+      <c r="K116" t="n">
         <v>219101</v>
-      </c>
-      <c r="K116" t="n">
-        <v>1357111594</v>
       </c>
       <c r="L116" t="n">
         <v>-0.0003236245954691963</v>
@@ -5346,10 +5346,10 @@
         <v>-1.084493363548077</v>
       </c>
       <c r="J117" t="n">
+        <v>3444</v>
+      </c>
+      <c r="K117" t="n">
         <v>211162</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1295531660.5</v>
       </c>
       <c r="L117" t="n">
         <v>-0.01084493363548078</v>
@@ -5388,10 +5388,10 @@
         <v>-0.7854688267059351</v>
       </c>
       <c r="J118" t="n">
+        <v>4160</v>
+      </c>
+      <c r="K118" t="n">
         <v>253480</v>
-      </c>
-      <c r="K118" t="n">
-        <v>1546544850</v>
       </c>
       <c r="L118" t="n">
         <v>-0.007854688267059373</v>
@@ -5430,10 +5430,10 @@
         <v>-1.863763813293753</v>
       </c>
       <c r="J119" t="n">
+        <v>7466</v>
+      </c>
+      <c r="K119" t="n">
         <v>447335</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2686694010</v>
       </c>
       <c r="L119" t="n">
         <v>-0.01863763813293751</v>
@@ -5472,10 +5472,10 @@
         <v>1.949579831932767</v>
       </c>
       <c r="J120" t="n">
+        <v>5700</v>
+      </c>
+      <c r="K120" t="n">
         <v>343973</v>
-      </c>
-      <c r="K120" t="n">
-        <v>2078972812</v>
       </c>
       <c r="L120" t="n">
         <v>0.01949579831932757</v>
@@ -5514,10 +5514,10 @@
         <v>0.3626772172766337</v>
       </c>
       <c r="J121" t="n">
+        <v>4346</v>
+      </c>
+      <c r="K121" t="n">
         <v>265045</v>
-      </c>
-      <c r="K121" t="n">
-        <v>1617569635</v>
       </c>
       <c r="L121" t="n">
         <v>0.003626772172766302</v>
@@ -5556,10 +5556,10 @@
         <v>2.431011826544016</v>
       </c>
       <c r="J122" t="n">
+        <v>7103</v>
+      </c>
+      <c r="K122" t="n">
         <v>439862</v>
-      </c>
-      <c r="K122" t="n">
-        <v>2723735469.5</v>
       </c>
       <c r="L122" t="n">
         <v>0.02431011826544016</v>
@@ -5598,10 +5598,10 @@
         <v>-0.4329698524695254</v>
       </c>
       <c r="J123" t="n">
+        <v>4127</v>
+      </c>
+      <c r="K123" t="n">
         <v>257308</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1605537593</v>
       </c>
       <c r="L123" t="n">
         <v>-0.004329698524695225</v>
@@ -5640,10 +5640,10 @@
         <v>-0.0161056530842408</v>
       </c>
       <c r="J124" t="n">
+        <v>3259</v>
+      </c>
+      <c r="K124" t="n">
         <v>202776</v>
-      </c>
-      <c r="K124" t="n">
-        <v>1259289654</v>
       </c>
       <c r="L124" t="n">
         <v>-0.0001610565308424183</v>
@@ -5682,10 +5682,10 @@
         <v>-0.2255154639175267</v>
       </c>
       <c r="J125" t="n">
+        <v>4110</v>
+      </c>
+      <c r="K125" t="n">
         <v>254831</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1574664456.75</v>
       </c>
       <c r="L125" t="n">
         <v>-0.00225515463917525</v>
@@ -5724,10 +5724,10 @@
         <v>-1.323861801743623</v>
       </c>
       <c r="J126" t="n">
+        <v>2964</v>
+      </c>
+      <c r="K126" t="n">
         <v>182306</v>
-      </c>
-      <c r="K126" t="n">
-        <v>1120817288</v>
       </c>
       <c r="L126" t="n">
         <v>-0.0132386180174362</v>
@@ -5766,10 +5766,10 @@
         <v>-0.245418848167537</v>
       </c>
       <c r="J127" t="n">
+        <v>3253</v>
+      </c>
+      <c r="K127" t="n">
         <v>198530</v>
-      </c>
-      <c r="K127" t="n">
-        <v>1212621240</v>
       </c>
       <c r="L127" t="n">
         <v>-0.002454188481675335</v>
@@ -5808,10 +5808,10 @@
         <v>0.4592422502870283</v>
       </c>
       <c r="J128" t="n">
+        <v>2951</v>
+      </c>
+      <c r="K128" t="n">
         <v>180408</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1103736144</v>
       </c>
       <c r="L128" t="n">
         <v>0.004592422502870175</v>
@@ -5850,10 +5850,10 @@
         <v>0.6040816326530571</v>
       </c>
       <c r="J129" t="n">
+        <v>3765</v>
+      </c>
+      <c r="K129" t="n">
         <v>231176</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1417686820</v>
       </c>
       <c r="L129" t="n">
         <v>0.00604081632653064</v>
@@ -5892,10 +5892,10 @@
         <v>1.363193768257065</v>
       </c>
       <c r="J130" t="n">
+        <v>8134</v>
+      </c>
+      <c r="K130" t="n">
         <v>508618</v>
-      </c>
-      <c r="K130" t="n">
-        <v>3185601688.5</v>
       </c>
       <c r="L130" t="n">
         <v>0.01363193768257065</v>
@@ -5934,10 +5934,10 @@
         <v>0.9926352865834093</v>
       </c>
       <c r="J131" t="n">
+        <v>7872</v>
+      </c>
+      <c r="K131" t="n">
         <v>493593</v>
-      </c>
-      <c r="K131" t="n">
-        <v>3107784926.25</v>
       </c>
       <c r="L131" t="n">
         <v>0.009926352865833987</v>
@@ -5976,10 +5976,10 @@
         <v>0.4755865567533358</v>
       </c>
       <c r="J132" t="n">
+        <v>4567</v>
+      </c>
+      <c r="K132" t="n">
         <v>288960</v>
-      </c>
-      <c r="K132" t="n">
-        <v>1823048640</v>
       </c>
       <c r="L132" t="n">
         <v>0.004755865567533268</v>
@@ -6018,10 +6018,10 @@
         <v>0.03155569580308618</v>
       </c>
       <c r="J133" t="n">
+        <v>3892</v>
+      </c>
+      <c r="K133" t="n">
         <v>247061</v>
-      </c>
-      <c r="K133" t="n">
-        <v>1568899115.25</v>
       </c>
       <c r="L133" t="n">
         <v>0.0003155569580308715</v>
@@ -6060,10 +6060,10 @@
         <v>-0.1892744479495228</v>
       </c>
       <c r="J134" t="n">
+        <v>4988</v>
+      </c>
+      <c r="K134" t="n">
         <v>315629</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1989251772.5</v>
       </c>
       <c r="L134" t="n">
         <v>-0.001892744479495279</v>
@@ -6102,10 +6102,10 @@
         <v>-3.002528445006319</v>
       </c>
       <c r="J135" t="n">
+        <v>4676</v>
+      </c>
+      <c r="K135" t="n">
         <v>290072</v>
-      </c>
-      <c r="K135" t="n">
-        <v>1799316616</v>
       </c>
       <c r="L135" t="n">
         <v>-0.03002528445006314</v>
@@ -6144,10 +6144,10 @@
         <v>-3.633105246008478</v>
       </c>
       <c r="J136" t="n">
+        <v>8691</v>
+      </c>
+      <c r="K136" t="n">
         <v>523785</v>
-      </c>
-      <c r="K136" t="n">
-        <v>3151876237.5</v>
       </c>
       <c r="L136" t="n">
         <v>-0.03633105246008483</v>
@@ -6186,10 +6186,10 @@
         <v>1.944209636517326</v>
       </c>
       <c r="J137" t="n">
+        <v>5523</v>
+      </c>
+      <c r="K137" t="n">
         <v>330418</v>
-      </c>
-      <c r="K137" t="n">
-        <v>1978047357</v>
       </c>
       <c r="L137" t="n">
         <v>0.01944209636517336</v>
@@ -6228,10 +6228,10 @@
         <v>-0.4975124378109406</v>
       </c>
       <c r="J138" t="n">
+        <v>2987</v>
+      </c>
+      <c r="K138" t="n">
         <v>179309</v>
-      </c>
-      <c r="K138" t="n">
-        <v>1078409153.25</v>
       </c>
       <c r="L138" t="n">
         <v>-0.00497512437810943</v>
@@ -6270,10 +6270,10 @@
         <v>1.416666666666669</v>
       </c>
       <c r="J139" t="n">
+        <v>4769</v>
+      </c>
+      <c r="K139" t="n">
         <v>288358</v>
-      </c>
-      <c r="K139" t="n">
-        <v>1746079779.5</v>
       </c>
       <c r="L139" t="n">
         <v>0.01416666666666666</v>
@@ -6312,10 +6312,10 @@
         <v>0.131470829909611</v>
       </c>
       <c r="J140" t="n">
+        <v>3889</v>
+      </c>
+      <c r="K140" t="n">
         <v>236709</v>
-      </c>
-      <c r="K140" t="n">
-        <v>1441380278.25</v>
       </c>
       <c r="L140" t="n">
         <v>0.001314708299096079</v>
@@ -6354,10 +6354,10 @@
         <v>1.427868045297879</v>
       </c>
       <c r="J141" t="n">
+        <v>5368</v>
+      </c>
+      <c r="K141" t="n">
         <v>329191</v>
-      </c>
-      <c r="K141" t="n">
-        <v>2024936138.75</v>
       </c>
       <c r="L141" t="n">
         <v>0.01427868045297886</v>
@@ -6396,10 +6396,10 @@
         <v>-0.9223300970873791</v>
       </c>
       <c r="J142" t="n">
+        <v>4077</v>
+      </c>
+      <c r="K142" t="n">
         <v>250502</v>
-      </c>
-      <c r="K142" t="n">
-        <v>1540462049</v>
       </c>
       <c r="L142" t="n">
         <v>-0.00922330097087376</v>
@@ -6438,10 +6438,10 @@
         <v>0.2776416789155671</v>
       </c>
       <c r="J143" t="n">
+        <v>2531</v>
+      </c>
+      <c r="K143" t="n">
         <v>155182</v>
-      </c>
-      <c r="K143" t="n">
-        <v>951692410.5</v>
       </c>
       <c r="L143" t="n">
         <v>0.002776416789155745</v>
@@ -6480,10 +6480,10 @@
         <v>-0.5537459283387562</v>
       </c>
       <c r="J144" t="n">
+        <v>3503</v>
+      </c>
+      <c r="K144" t="n">
         <v>214308</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1310600574</v>
       </c>
       <c r="L144" t="n">
         <v>-0.005537459283387558</v>
@@ -6522,10 +6522,10 @@
         <v>-0.9007533573534298</v>
       </c>
       <c r="J145" t="n">
+        <v>4701</v>
+      </c>
+      <c r="K145" t="n">
         <v>285752</v>
-      </c>
-      <c r="K145" t="n">
-        <v>1737729350</v>
       </c>
       <c r="L145" t="n">
         <v>-0.009007533573534343</v>
@@ -6564,10 +6564,10 @@
         <v>-0.5453644025780835</v>
       </c>
       <c r="J146" t="n">
+        <v>4201</v>
+      </c>
+      <c r="K146" t="n">
         <v>253305</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1526669235</v>
       </c>
       <c r="L146" t="n">
         <v>-0.005453644025780857</v>
@@ -6606,10 +6606,10 @@
         <v>-1.013625789298769</v>
       </c>
       <c r="J147" t="n">
+        <v>4481</v>
+      </c>
+      <c r="K147" t="n">
         <v>268279</v>
-      </c>
-      <c r="K147" t="n">
-        <v>1606924140.25</v>
       </c>
       <c r="L147" t="n">
         <v>-0.01013625789298767</v>
@@ -6648,10 +6648,10 @@
         <v>5.892227631358063</v>
       </c>
       <c r="J148" t="n">
+        <v>13824</v>
+      </c>
+      <c r="K148" t="n">
         <v>851170</v>
-      </c>
-      <c r="K148" t="n">
-        <v>5247888635</v>
       </c>
       <c r="L148" t="n">
         <v>0.0589222763135806</v>
@@ -6690,10 +6690,10 @@
         <v>-0.03170577045021564</v>
       </c>
       <c r="J149" t="n">
+        <v>7333</v>
+      </c>
+      <c r="K149" t="n">
         <v>463525</v>
-      </c>
-      <c r="K149" t="n">
-        <v>2923683937.5</v>
       </c>
       <c r="L149" t="n">
         <v>-0.0003170577045021883</v>
@@ -6732,10 +6732,10 @@
         <v>1.25277513479226</v>
       </c>
       <c r="J150" t="n">
+        <v>8271</v>
+      </c>
+      <c r="K150" t="n">
         <v>524652</v>
-      </c>
-      <c r="K150" t="n">
-        <v>3340196958</v>
       </c>
       <c r="L150" t="n">
         <v>0.0125277513479225</v>
@@ -6774,10 +6774,10 @@
         <v>-0.3915426781519186</v>
       </c>
       <c r="J151" t="n">
+        <v>6963</v>
+      </c>
+      <c r="K151" t="n">
         <v>447749</v>
-      </c>
-      <c r="K151" t="n">
-        <v>2873205333</v>
       </c>
       <c r="L151" t="n">
         <v>-0.003915426781519238</v>
@@ -6816,10 +6816,10 @@
         <v>0.2830188679245279</v>
       </c>
       <c r="J152" t="n">
+        <v>6695</v>
+      </c>
+      <c r="K152" t="n">
         <v>426358</v>
-      </c>
-      <c r="K152" t="n">
-        <v>2711210522</v>
       </c>
       <c r="L152" t="n">
         <v>0.002830188679245227</v>
@@ -6858,10 +6858,10 @@
         <v>0.1097522734399503</v>
       </c>
       <c r="J153" t="n">
+        <v>6702</v>
+      </c>
+      <c r="K153" t="n">
         <v>428770</v>
-      </c>
-      <c r="K153" t="n">
-        <v>2738339605</v>
       </c>
       <c r="L153" t="n">
         <v>0.001097522734399448</v>
@@ -6900,10 +6900,10 @@
         <v>1.049334377447133</v>
       </c>
       <c r="J154" t="n">
+        <v>11494</v>
+      </c>
+      <c r="K154" t="n">
         <v>740340</v>
-      </c>
-      <c r="K154" t="n">
-        <v>4788148950</v>
       </c>
       <c r="L154" t="n">
         <v>0.01049334377447142</v>
@@ -6942,10 +6942,10 @@
         <v>-1.41041537507749</v>
       </c>
       <c r="J155" t="n">
+        <v>9820</v>
+      </c>
+      <c r="K155" t="n">
         <v>629255</v>
-      </c>
-      <c r="K155" t="n">
-        <v>4042334120</v>
       </c>
       <c r="L155" t="n">
         <v>-0.01410415375077489</v>
@@ -6984,10 +6984,10 @@
         <v>-0.6917151391290642</v>
       </c>
       <c r="J156" t="n">
+        <v>7402</v>
+      </c>
+      <c r="K156" t="n">
         <v>467612</v>
-      </c>
-      <c r="K156" t="n">
-        <v>2956243064</v>
       </c>
       <c r="L156" t="n">
         <v>-0.006917151391290677</v>
@@ -7026,10 +7026,10 @@
         <v>-1.947126800696539</v>
       </c>
       <c r="J157" t="n">
+        <v>8361</v>
+      </c>
+      <c r="K157" t="n">
         <v>523786</v>
-      </c>
-      <c r="K157" t="n">
-        <v>3279816985.5</v>
       </c>
       <c r="L157" t="n">
         <v>-0.01947126800696541</v>
@@ -7068,10 +7068,10 @@
         <v>-1.323861801743623</v>
       </c>
       <c r="J158" t="n">
+        <v>7711</v>
+      </c>
+      <c r="K158" t="n">
         <v>473891</v>
-      </c>
-      <c r="K158" t="n">
-        <v>2913955759</v>
       </c>
       <c r="L158" t="n">
         <v>-0.0132386180174362</v>
@@ -7110,10 +7110,10 @@
         <v>-1.014397905759158</v>
       </c>
       <c r="J159" t="n">
+        <v>7034</v>
+      </c>
+      <c r="K159" t="n">
         <v>427755</v>
-      </c>
-      <c r="K159" t="n">
-        <v>2605883460</v>
       </c>
       <c r="L159" t="n">
         <v>-0.01014397905759157</v>
@@ -7152,10 +7152,10 @@
         <v>-0.6611570247933861</v>
       </c>
       <c r="J160" t="n">
+        <v>9055</v>
+      </c>
+      <c r="K160" t="n">
         <v>546035</v>
-      </c>
-      <c r="K160" t="n">
-        <v>3294638681.25</v>
       </c>
       <c r="L160" t="n">
         <v>-0.006611570247933907</v>
@@ -7194,10 +7194,10 @@
         <v>-1.098169717138109</v>
       </c>
       <c r="J161" t="n">
+        <v>8966</v>
+      </c>
+      <c r="K161" t="n">
         <v>537068</v>
-      </c>
-      <c r="K161" t="n">
-        <v>3215157582</v>
       </c>
       <c r="L161" t="n">
         <v>-0.01098169717138109</v>
@@ -7236,10 +7236,10 @@
         <v>-0.7570659488559821</v>
       </c>
       <c r="J162" t="n">
+        <v>13613</v>
+      </c>
+      <c r="K162" t="n">
         <v>808043</v>
-      </c>
-      <c r="K162" t="n">
-        <v>4802805581.25</v>
       </c>
       <c r="L162" t="n">
         <v>-0.007570659488559839</v>
@@ -7278,10 +7278,10 @@
         <v>-1.40701813866758</v>
       </c>
       <c r="J163" t="n">
+        <v>12417</v>
+      </c>
+      <c r="K163" t="n">
         <v>727329</v>
-      </c>
-      <c r="K163" t="n">
-        <v>4261420611</v>
       </c>
       <c r="L163" t="n">
         <v>-0.01407018138667582</v>
@@ -7320,10 +7320,10 @@
         <v>-1.650618982118284</v>
       </c>
       <c r="J164" t="n">
+        <v>11026</v>
+      </c>
+      <c r="K164" t="n">
         <v>637255</v>
-      </c>
-      <c r="K164" t="n">
-        <v>3683652527.5</v>
       </c>
       <c r="L164" t="n">
         <v>-0.01650618982118279</v>
@@ -7362,10 +7362,10 @@
         <v>-1.136363636363646</v>
       </c>
       <c r="J165" t="n">
+        <v>15418</v>
+      </c>
+      <c r="K165" t="n">
         <v>878750</v>
-      </c>
-      <c r="K165" t="n">
-        <v>5010852187.5</v>
       </c>
       <c r="L165" t="n">
         <v>-0.01136363636363646</v>
@@ -7404,10 +7404,10 @@
         <v>2.758620689655177</v>
       </c>
       <c r="J166" t="n">
+        <v>19882</v>
+      </c>
+      <c r="K166" t="n">
         <v>1137825</v>
-      </c>
-      <c r="K166" t="n">
-        <v>6511488018.75</v>
       </c>
       <c r="L166" t="n">
         <v>0.02758620689655178</v>
@@ -7446,10 +7446,10 @@
         <v>0.08604371020477913</v>
       </c>
       <c r="J167" t="n">
+        <v>14670</v>
+      </c>
+      <c r="K167" t="n">
         <v>852045</v>
-      </c>
-      <c r="K167" t="n">
-        <v>4978285923.75</v>
       </c>
       <c r="L167" t="n">
         <v>0.0008604371020477508</v>
@@ -7488,10 +7488,10 @@
         <v>-2.871389270976607</v>
       </c>
       <c r="J168" t="n">
+        <v>10671</v>
+      </c>
+      <c r="K168" t="n">
         <v>609580</v>
-      </c>
-      <c r="K168" t="n">
-        <v>3488169155</v>
       </c>
       <c r="L168" t="n">
         <v>-0.0287138927097661</v>
@@ -7530,10 +7530,10 @@
         <v>1.734820322180911</v>
       </c>
       <c r="J169" t="n">
+        <v>8716</v>
+      </c>
+      <c r="K169" t="n">
         <v>498835</v>
-      </c>
-      <c r="K169" t="n">
-        <v>2851590277.5</v>
       </c>
       <c r="L169" t="n">
         <v>0.01734820322180908</v>
@@ -7572,10 +7572,10 @@
         <v>0.2262049765094877</v>
       </c>
       <c r="J170" t="n">
+        <v>8516</v>
+      </c>
+      <c r="K170" t="n">
         <v>489243</v>
-      </c>
-      <c r="K170" t="n">
-        <v>2798836892.25</v>
       </c>
       <c r="L170" t="n">
         <v>0.00226204976509492</v>
@@ -7614,10 +7614,10 @@
         <v>0.9722222222222138</v>
       </c>
       <c r="J171" t="n">
+        <v>8953</v>
+      </c>
+      <c r="K171" t="n">
         <v>517746</v>
-      </c>
-      <c r="K171" t="n">
-        <v>2995548919.5</v>
       </c>
       <c r="L171" t="n">
         <v>0.009722222222222188</v>
@@ -7656,10 +7656,10 @@
         <v>-1.461485557083897</v>
       </c>
       <c r="J172" t="n">
+        <v>6274</v>
+      </c>
+      <c r="K172" t="n">
         <v>360904</v>
-      </c>
-      <c r="K172" t="n">
-        <v>2079167944</v>
       </c>
       <c r="L172" t="n">
         <v>-0.01461485557083897</v>
@@ -7698,10 +7698,10 @@
         <v>0.2442854650148326</v>
       </c>
       <c r="J173" t="n">
+        <v>6356</v>
+      </c>
+      <c r="K173" t="n">
         <v>366117</v>
-      </c>
-      <c r="K173" t="n">
-        <v>2105996513.25</v>
       </c>
       <c r="L173" t="n">
         <v>0.002442854650148263</v>
@@ -7740,10 +7740,10 @@
         <v>1.653611836379453</v>
       </c>
       <c r="J174" t="n">
+        <v>11201</v>
+      </c>
+      <c r="K174" t="n">
         <v>648861</v>
-      </c>
-      <c r="K174" t="n">
-        <v>3762582723.75</v>
       </c>
       <c r="L174" t="n">
         <v>0.01653611836379443</v>
@@ -7782,10 +7782,10 @@
         <v>0.8561643835616438</v>
       </c>
       <c r="J175" t="n">
+        <v>9781</v>
+      </c>
+      <c r="K175" t="n">
         <v>573680</v>
-      </c>
-      <c r="K175" t="n">
-        <v>3378975200</v>
       </c>
       <c r="L175" t="n">
         <v>0.008561643835616417</v>
@@ -7824,10 +7824,10 @@
         <v>-0.271646859083186</v>
       </c>
       <c r="J176" t="n">
+        <v>5943</v>
+      </c>
+      <c r="K176" t="n">
         <v>348690</v>
-      </c>
-      <c r="K176" t="n">
-        <v>2051430442.5</v>
       </c>
       <c r="L176" t="n">
         <v>-0.002716468590831855</v>
@@ -7866,10 +7866,10 @@
         <v>-0.8682328907048095</v>
       </c>
       <c r="J177" t="n">
+        <v>5873</v>
+      </c>
+      <c r="K177" t="n">
         <v>343568</v>
-      </c>
-      <c r="K177" t="n">
-        <v>2011332964</v>
       </c>
       <c r="L177" t="n">
         <v>-0.00868232890704812</v>
@@ -7908,10 +7908,10 @@
         <v>-0.3778121243345335</v>
       </c>
       <c r="J178" t="n">
+        <v>5828</v>
+      </c>
+      <c r="K178" t="n">
         <v>338981</v>
-      </c>
-      <c r="K178" t="n">
-        <v>1970496553</v>
       </c>
       <c r="L178" t="n">
         <v>-0.003778121243345312</v>
@@ -7950,10 +7950,10 @@
         <v>-0.2585761075676583</v>
       </c>
       <c r="J179" t="n">
+        <v>7279</v>
+      </c>
+      <c r="K179" t="n">
         <v>421579</v>
-      </c>
-      <c r="K179" t="n">
-        <v>2441153199.5</v>
       </c>
       <c r="L179" t="n">
         <v>-0.00258576107567654</v>
@@ -7992,10 +7992,10 @@
         <v>-1.970273072934671</v>
       </c>
       <c r="J180" t="n">
+        <v>8884</v>
+      </c>
+      <c r="K180" t="n">
         <v>508987</v>
-      </c>
-      <c r="K180" t="n">
-        <v>2917513484</v>
       </c>
       <c r="L180" t="n">
         <v>-0.0197027307293467</v>
@@ -8034,10 +8034,10 @@
         <v>-0.2820874471085977</v>
       </c>
       <c r="J181" t="n">
+        <v>6426</v>
+      </c>
+      <c r="K181" t="n">
         <v>363641</v>
-      </c>
-      <c r="K181" t="n">
-        <v>2061389918.75</v>
       </c>
       <c r="L181" t="n">
         <v>-0.002820874471085921</v>
@@ -8076,10 +8076,10 @@
         <v>-3.571428571428577</v>
       </c>
       <c r="J182" t="n">
+        <v>13477</v>
+      </c>
+      <c r="K182" t="n">
         <v>742062</v>
-      </c>
-      <c r="K182" t="n">
-        <v>4088761620</v>
       </c>
       <c r="L182" t="n">
         <v>-0.03571428571428581</v>
@@ -8118,10 +8118,10 @@
         <v>-1.705170517051704</v>
       </c>
       <c r="J183" t="n">
+        <v>11105</v>
+      </c>
+      <c r="K183" t="n">
         <v>601399</v>
-      </c>
-      <c r="K183" t="n">
-        <v>3263942722.75</v>
       </c>
       <c r="L183" t="n">
         <v>-0.01705170517051702</v>
@@ -8160,10 +8160,10 @@
         <v>-1.175153889199781</v>
       </c>
       <c r="J184" t="n">
+        <v>8880</v>
+      </c>
+      <c r="K184" t="n">
         <v>471518</v>
-      </c>
-      <c r="K184" t="n">
-        <v>2508122121.5</v>
       </c>
       <c r="L184" t="n">
         <v>-0.01175153889199776</v>
@@ -8202,10 +8202,10 @@
         <v>1.396753491883734</v>
       </c>
       <c r="J185" t="n">
+        <v>9052</v>
+      </c>
+      <c r="K185" t="n">
         <v>484860</v>
-      </c>
-      <c r="K185" t="n">
-        <v>2606971005</v>
       </c>
       <c r="L185" t="n">
         <v>0.01396753491883729</v>
@@ -8244,10 +8244,10 @@
         <v>3.425167535368584</v>
       </c>
       <c r="J186" t="n">
+        <v>11527</v>
+      </c>
+      <c r="K186" t="n">
         <v>629119</v>
-      </c>
-      <c r="K186" t="n">
-        <v>3432315984.25</v>
       </c>
       <c r="L186" t="n">
         <v>0.0342516753536859</v>
@@ -8286,10 +8286,10 @@
         <v>-1.115910727141837</v>
       </c>
       <c r="J187" t="n">
+        <v>7769</v>
+      </c>
+      <c r="K187" t="n">
         <v>426233</v>
-      </c>
-      <c r="K187" t="n">
-        <v>2333092883.75</v>
       </c>
       <c r="L187" t="n">
         <v>-0.01115910727141833</v>
@@ -8328,10 +8328,10 @@
         <v>2.930469603203494</v>
       </c>
       <c r="J188" t="n">
+        <v>8469</v>
+      </c>
+      <c r="K188" t="n">
         <v>473605</v>
-      </c>
-      <c r="K188" t="n">
-        <v>2651003987.5</v>
       </c>
       <c r="L188" t="n">
         <v>0.02930469603203489</v>
@@ -8370,10 +8370,10 @@
         <v>-1.273209549071616</v>
       </c>
       <c r="J189" t="n">
+        <v>5722</v>
+      </c>
+      <c r="K189" t="n">
         <v>321259</v>
-      </c>
-      <c r="K189" t="n">
-        <v>1802503934.25</v>
       </c>
       <c r="L189" t="n">
         <v>-0.01273209549071619</v>
@@ -8412,10 +8412,10 @@
         <v>-0.9493104065914403</v>
       </c>
       <c r="J190" t="n">
+        <v>4801</v>
+      </c>
+      <c r="K190" t="n">
         <v>266691</v>
-      </c>
-      <c r="K190" t="n">
-        <v>1482601941.75</v>
       </c>
       <c r="L190" t="n">
         <v>-0.009493104065914415</v>
@@ -8454,10 +8454,10 @@
         <v>-0.3435804701627446</v>
       </c>
       <c r="J191" t="n">
+        <v>4423</v>
+      </c>
+      <c r="K191" t="n">
         <v>244164</v>
-      </c>
-      <c r="K191" t="n">
-        <v>1348945059</v>
       </c>
       <c r="L191" t="n">
         <v>-0.00343580470162741</v>
@@ -8496,10 +8496,10 @@
         <v>0.8709853021230338</v>
       </c>
       <c r="J192" t="n">
+        <v>5555</v>
+      </c>
+      <c r="K192" t="n">
         <v>307751</v>
-      </c>
-      <c r="K192" t="n">
-        <v>1703170971.75</v>
       </c>
       <c r="L192" t="n">
         <v>0.008709853021230396</v>
@@ -8538,10 +8538,10 @@
         <v>1.277208130958794</v>
       </c>
       <c r="J193" t="n">
+        <v>9003</v>
+      </c>
+      <c r="K193" t="n">
         <v>504111</v>
-      </c>
-      <c r="K193" t="n">
-        <v>2833229847.75</v>
       </c>
       <c r="L193" t="n">
         <v>0.01277208130958796</v>
@@ -8580,10 +8580,10 @@
         <v>1.03019538188278</v>
       </c>
       <c r="J194" t="n">
+        <v>6961</v>
+      </c>
+      <c r="K194" t="n">
         <v>393793</v>
-      </c>
-      <c r="K194" t="n">
-        <v>2227293208</v>
       </c>
       <c r="L194" t="n">
         <v>0.01030195381882781</v>
@@ -8622,10 +8622,10 @@
         <v>-1.51195499296765</v>
       </c>
       <c r="J195" t="n">
+        <v>6126</v>
+      </c>
+      <c r="K195" t="n">
         <v>343647</v>
-      </c>
-      <c r="K195" t="n">
-        <v>1934131227.75</v>
       </c>
       <c r="L195" t="n">
         <v>-0.01511954992967646</v>
@@ -8664,10 +8664,10 @@
         <v>-1.570867547304539</v>
       </c>
       <c r="J196" t="n">
+        <v>6241</v>
+      </c>
+      <c r="K196" t="n">
         <v>347395</v>
-      </c>
-      <c r="K196" t="n">
-        <v>1937943007.5</v>
       </c>
       <c r="L196" t="n">
         <v>-0.01570867547304533</v>
@@ -8706,10 +8706,10 @@
         <v>-4.280014508523757</v>
       </c>
       <c r="J197" t="n">
+        <v>9119</v>
+      </c>
+      <c r="K197" t="n">
         <v>487702</v>
-      </c>
-      <c r="K197" t="n">
-        <v>2605791786</v>
       </c>
       <c r="L197" t="n">
         <v>-0.04280014508523755</v>
@@ -8748,10 +8748,10 @@
         <v>1.629405077680939</v>
       </c>
       <c r="J198" t="n">
+        <v>6517</v>
+      </c>
+      <c r="K198" t="n">
         <v>348355</v>
-      </c>
-      <c r="K198" t="n">
-        <v>1858996457.5</v>
       </c>
       <c r="L198" t="n">
         <v>0.01629405077680945</v>
@@ -8790,10 +8790,10 @@
         <v>0.8575689783743491</v>
       </c>
       <c r="J199" t="n">
+        <v>7614</v>
+      </c>
+      <c r="K199" t="n">
         <v>411526</v>
-      </c>
-      <c r="K199" t="n">
-        <v>2230470920</v>
       </c>
       <c r="L199" t="n">
         <v>0.008575689783743456</v>
@@ -8832,10 +8832,10 @@
         <v>-4.565619223659887</v>
       </c>
       <c r="J200" t="n">
+        <v>12380</v>
+      </c>
+      <c r="K200" t="n">
         <v>649417</v>
-      </c>
-      <c r="K200" t="n">
-        <v>3418368733.75</v>
       </c>
       <c r="L200" t="n">
         <v>-0.04565619223659889</v>
@@ -8874,10 +8874,10 @@
         <v>6.875847375556841</v>
       </c>
       <c r="J201" t="n">
+        <v>18618</v>
+      </c>
+      <c r="K201" t="n">
         <v>991196</v>
-      </c>
-      <c r="K201" t="n">
-        <v>5279853293</v>
       </c>
       <c r="L201" t="n">
         <v>0.06875847375556843</v>
@@ -8916,10 +8916,10 @@
         <v>1.05110547299746</v>
       </c>
       <c r="J202" t="n">
+        <v>12621</v>
+      </c>
+      <c r="K202" t="n">
         <v>697271</v>
-      </c>
-      <c r="K202" t="n">
-        <v>3855908630</v>
       </c>
       <c r="L202" t="n">
         <v>0.01051105472997449</v>
@@ -8958,10 +8958,10 @@
         <v>-0.9684361549497833</v>
       </c>
       <c r="J203" t="n">
+        <v>12476</v>
+      </c>
+      <c r="K203" t="n">
         <v>692924</v>
-      </c>
-      <c r="K203" t="n">
-        <v>3874484546</v>
       </c>
       <c r="L203" t="n">
         <v>-0.009684361549497811</v>
@@ -9000,10 +9000,10 @@
         <v>4.545454545454542</v>
       </c>
       <c r="J204" t="n">
+        <v>17678</v>
+      </c>
+      <c r="K204" t="n">
         <v>1005517</v>
-      </c>
-      <c r="K204" t="n">
-        <v>5709828284.5</v>
       </c>
       <c r="L204" t="n">
         <v>0.04545454545454541</v>
@@ -9042,10 +9042,10 @@
         <v>-0.6235925861770301</v>
       </c>
       <c r="J205" t="n">
+        <v>13295</v>
+      </c>
+      <c r="K205" t="n">
         <v>765170</v>
-      </c>
-      <c r="K205" t="n">
-        <v>4408718247.5</v>
       </c>
       <c r="L205" t="n">
         <v>-0.006235925861770353</v>
@@ -9084,10 +9084,10 @@
         <v>-1.72564057869966</v>
       </c>
       <c r="J206" t="n">
+        <v>8026</v>
+      </c>
+      <c r="K206" t="n">
         <v>454916</v>
-      </c>
-      <c r="K206" t="n">
-        <v>2575393205</v>
       </c>
       <c r="L206" t="n">
         <v>-0.01725640578699661</v>
@@ -9126,10 +9126,10 @@
         <v>-0.4611564384533613</v>
       </c>
       <c r="J207" t="n">
+        <v>7129</v>
+      </c>
+      <c r="K207" t="n">
         <v>401467</v>
-      </c>
-      <c r="K207" t="n">
-        <v>2253032804</v>
       </c>
       <c r="L207" t="n">
         <v>-0.004611564384533584</v>
@@ -9168,10 +9168,10 @@
         <v>2.36992159657877</v>
       </c>
       <c r="J208" t="n">
+        <v>12834</v>
+      </c>
+      <c r="K208" t="n">
         <v>734463</v>
-      </c>
-      <c r="K208" t="n">
-        <v>4186622715.75</v>
       </c>
       <c r="L208" t="n">
         <v>0.02369921596578761</v>
@@ -9210,10 +9210,10 @@
         <v>-0.852915578764146</v>
       </c>
       <c r="J209" t="n">
+        <v>8443</v>
+      </c>
+      <c r="K209" t="n">
         <v>480755</v>
-      </c>
-      <c r="K209" t="n">
-        <v>2747034070</v>
       </c>
       <c r="L209" t="n">
         <v>-0.008529155787641463</v>
@@ -9252,10 +9252,10 @@
         <v>0.1755617977528115</v>
       </c>
       <c r="J210" t="n">
+        <v>10262</v>
+      </c>
+      <c r="K210" t="n">
         <v>587795</v>
-      </c>
-      <c r="K210" t="n">
-        <v>3372473812.5</v>
       </c>
       <c r="L210" t="n">
         <v>0.001755617977528212</v>
@@ -9294,10 +9294,10 @@
         <v>-3.259726603575183</v>
       </c>
       <c r="J211" t="n">
+        <v>14241</v>
+      </c>
+      <c r="K211" t="n">
         <v>796044</v>
-      </c>
-      <c r="K211" t="n">
-        <v>4446900795</v>
       </c>
       <c r="L211" t="n">
         <v>-0.03259726603575186</v>
@@ -9336,10 +9336,10 @@
         <v>1.775362318840574</v>
       </c>
       <c r="J212" t="n">
+        <v>10301</v>
+      </c>
+      <c r="K212" t="n">
         <v>574457</v>
-      </c>
-      <c r="K212" t="n">
-        <v>3197427662</v>
       </c>
       <c r="L212" t="n">
         <v>0.01775362318840568</v>
@@ -9378,10 +9378,10 @@
         <v>2.758988964044139</v>
       </c>
       <c r="J213" t="n">
+        <v>17800</v>
+      </c>
+      <c r="K213" t="n">
         <v>1029480</v>
-      </c>
-      <c r="K213" t="n">
-        <v>5949364920</v>
       </c>
       <c r="L213" t="n">
         <v>0.0275898896404414</v>
@@ -9420,10 +9420,10 @@
         <v>-0.4503724233500745</v>
       </c>
       <c r="J214" t="n">
+        <v>9991</v>
+      </c>
+      <c r="K214" t="n">
         <v>576718</v>
-      </c>
-      <c r="K214" t="n">
-        <v>3322904936.5</v>
       </c>
       <c r="L214" t="n">
         <v>-0.004503724233500761</v>
@@ -9462,10 +9462,10 @@
         <v>-1.983643640160085</v>
       </c>
       <c r="J215" t="n">
+        <v>11143</v>
+      </c>
+      <c r="K215" t="n">
         <v>632524</v>
-      </c>
-      <c r="K215" t="n">
-        <v>3585462294</v>
       </c>
       <c r="L215" t="n">
         <v>-0.01983643640160082</v>
@@ -9504,10 +9504,10 @@
         <v>0.01775252973549639</v>
       </c>
       <c r="J216" t="n">
+        <v>7687</v>
+      </c>
+      <c r="K216" t="n">
         <v>433049</v>
-      </c>
-      <c r="K216" t="n">
-        <v>2437849345.5</v>
       </c>
       <c r="L216" t="n">
         <v>0.0001775252973550412</v>
@@ -9546,10 +9546,10 @@
         <v>-1.047213347532842</v>
       </c>
       <c r="J217" t="n">
+        <v>7721</v>
+      </c>
+      <c r="K217" t="n">
         <v>432751</v>
-      </c>
-      <c r="K217" t="n">
-        <v>2427841297.75</v>
       </c>
       <c r="L217" t="n">
         <v>-0.01047213347532838</v>
@@ -9588,10 +9588,10 @@
         <v>-0.5560538116591969</v>
       </c>
       <c r="J218" t="n">
+        <v>9430</v>
+      </c>
+      <c r="K218" t="n">
         <v>523563</v>
-      </c>
-      <c r="K218" t="n">
-        <v>2904727524</v>
       </c>
       <c r="L218" t="n">
         <v>-0.005560538116591962</v>
@@ -9630,10 +9630,10 @@
         <v>1.731601731601733</v>
       </c>
       <c r="J219" t="n">
+        <v>17147</v>
+      </c>
+      <c r="K219" t="n">
         <v>963938</v>
-      </c>
-      <c r="K219" t="n">
-        <v>5456371049</v>
       </c>
       <c r="L219" t="n">
         <v>0.0173160173160174</v>
@@ -9672,10 +9672,10 @@
         <v>-0.6205673758865273</v>
       </c>
       <c r="J220" t="n">
+        <v>9912</v>
+      </c>
+      <c r="K220" t="n">
         <v>557798</v>
-      </c>
-      <c r="K220" t="n">
-        <v>3132314669</v>
       </c>
       <c r="L220" t="n">
         <v>-0.006205673758865271</v>
@@ -9714,10 +9714,10 @@
         <v>-1.195361284567341</v>
       </c>
       <c r="J221" t="n">
+        <v>8175</v>
+      </c>
+      <c r="K221" t="n">
         <v>455530</v>
-      </c>
-      <c r="K221" t="n">
-        <v>2536277157.5</v>
       </c>
       <c r="L221" t="n">
         <v>-0.01195361284567342</v>
@@ -9756,10 +9756,10 @@
         <v>-0.975081256771396</v>
       </c>
       <c r="J222" t="n">
+        <v>16388</v>
+      </c>
+      <c r="K222" t="n">
         <v>903120</v>
-      </c>
-      <c r="K222" t="n">
-        <v>5020669860</v>
       </c>
       <c r="L222" t="n">
         <v>-0.009750812567713929</v>
@@ -9798,10 +9798,10 @@
         <v>0.2735229759299755</v>
       </c>
       <c r="J223" t="n">
+        <v>10772</v>
+      </c>
+      <c r="K223" t="n">
         <v>591509</v>
-      </c>
-      <c r="K223" t="n">
-        <v>3239990547.5</v>
       </c>
       <c r="L223" t="n">
         <v>0.00273522975929974</v>
@@ -9840,10 +9840,10 @@
         <v>-2.018548827059464</v>
       </c>
       <c r="J224" t="n">
+        <v>13083</v>
+      </c>
+      <c r="K224" t="n">
         <v>712485</v>
-      </c>
-      <c r="K224" t="n">
-        <v>3878946461.25</v>
       </c>
       <c r="L224" t="n">
         <v>-0.02018548827059463</v>
@@ -9882,10 +9882,10 @@
         <v>-0.4639940608760207</v>
       </c>
       <c r="J225" t="n">
+        <v>12373</v>
+      </c>
+      <c r="K225" t="n">
         <v>665748</v>
-      </c>
-      <c r="K225" t="n">
-        <v>3580392744</v>
       </c>
       <c r="L225" t="n">
         <v>-0.004639940608760162</v>
@@ -9924,10 +9924,10 @@
         <v>0.09323140033562774</v>
       </c>
       <c r="J226" t="n">
+        <v>11593</v>
+      </c>
+      <c r="K226" t="n">
         <v>623452</v>
-      </c>
-      <c r="K226" t="n">
-        <v>3357133157</v>
       </c>
       <c r="L226" t="n">
         <v>0.0009323140033563604</v>
@@ -9966,10 +9966,10 @@
         <v>-1.639344262295087</v>
       </c>
       <c r="J227" t="n">
+        <v>15043</v>
+      </c>
+      <c r="K227" t="n">
         <v>802415</v>
-      </c>
-      <c r="K227" t="n">
-        <v>4278476780</v>
       </c>
       <c r="L227" t="n">
         <v>-0.01639344262295084</v>
@@ -10008,10 +10008,10 @@
         <v>1.363636363636375</v>
       </c>
       <c r="J228" t="n">
+        <v>19245</v>
+      </c>
+      <c r="K228" t="n">
         <v>1023063</v>
-      </c>
-      <c r="K228" t="n">
-        <v>5428116512.25</v>
       </c>
       <c r="L228" t="n">
         <v>0.01363636363636367</v>
@@ -10050,10 +10050,10 @@
         <v>4.839312406576973</v>
       </c>
       <c r="J229" t="n">
+        <v>44973</v>
+      </c>
+      <c r="K229" t="n">
         <v>2465400</v>
-      </c>
-      <c r="K229" t="n">
-        <v>13637360100</v>
       </c>
       <c r="L229" t="n">
         <v>0.04839312406576979</v>
@@ -10092,10 +10092,10 @@
         <v>-0.4455533772945999</v>
       </c>
       <c r="J230" t="n">
+        <v>23717</v>
+      </c>
+      <c r="K230" t="n">
         <v>1327791</v>
-      </c>
-      <c r="K230" t="n">
-        <v>7465172949.75</v>
       </c>
       <c r="L230" t="n">
         <v>-0.004455533772946052</v>
@@ -10134,10 +10134,10 @@
         <v>-2.756892230576439</v>
       </c>
       <c r="J231" t="n">
+        <v>16659</v>
+      </c>
+      <c r="K231" t="n">
         <v>917227</v>
-      </c>
-      <c r="K231" t="n">
-        <v>5070889469.5</v>
       </c>
       <c r="L231" t="n">
         <v>-0.02756892230576435</v>
@@ -10176,10 +10176,10 @@
         <v>-0.6075110456553724</v>
       </c>
       <c r="J232" t="n">
+        <v>14176</v>
+      </c>
+      <c r="K232" t="n">
         <v>765989</v>
-      </c>
-      <c r="K232" t="n">
-        <v>4164682193</v>
       </c>
       <c r="L232" t="n">
         <v>-0.006075110456553734</v>
@@ -10218,10 +10218,10 @@
         <v>-2.889423967401374</v>
       </c>
       <c r="J233" t="n">
+        <v>14812</v>
+      </c>
+      <c r="K233" t="n">
         <v>786609</v>
-      </c>
-      <c r="K233" t="n">
-        <v>4172960745</v>
       </c>
       <c r="L233" t="n">
         <v>-0.02889423967401372</v>
@@ -10260,10 +10260,10 @@
         <v>-1.602136181575427</v>
       </c>
       <c r="J234" t="n">
+        <v>13458</v>
+      </c>
+      <c r="K234" t="n">
         <v>699095</v>
-      </c>
-      <c r="K234" t="n">
-        <v>3637566058.75</v>
       </c>
       <c r="L234" t="n">
         <v>-0.01602136181575431</v>
@@ -10302,10 +10302,10 @@
         <v>-1.240550494281839</v>
       </c>
       <c r="J235" t="n">
+        <v>16144</v>
+      </c>
+      <c r="K235" t="n">
         <v>827046</v>
-      </c>
-      <c r="K235" t="n">
-        <v>4234475520</v>
       </c>
       <c r="L235" t="n">
         <v>-0.01240550494281834</v>
@@ -10344,10 +10344,10 @@
         <v>0.9813542688910696</v>
       </c>
       <c r="J236" t="n">
+        <v>19399</v>
+      </c>
+      <c r="K236" t="n">
         <v>994025</v>
-      </c>
-      <c r="K236" t="n">
-        <v>5122956343.75</v>
       </c>
       <c r="L236" t="n">
         <v>0.00981354268891077</v>
@@ -10386,10 +10386,10 @@
         <v>-1.904761904761912</v>
       </c>
       <c r="J237" t="n">
+        <v>13284</v>
+      </c>
+      <c r="K237" t="n">
         <v>677620</v>
-      </c>
-      <c r="K237" t="n">
-        <v>3455862000</v>
       </c>
       <c r="L237" t="n">
         <v>-0.01904761904761909</v>
@@ -10428,10 +10428,10 @@
         <v>-2.060630077273626</v>
       </c>
       <c r="J238" t="n">
+        <v>16862</v>
+      </c>
+      <c r="K238" t="n">
         <v>838355</v>
-      </c>
-      <c r="K238" t="n">
-        <v>4159917510</v>
       </c>
       <c r="L238" t="n">
         <v>-0.02060630077273629</v>
@@ -10470,10 +10470,10 @@
         <v>-0.4653044709690408</v>
       </c>
       <c r="J239" t="n">
+        <v>14525</v>
+      </c>
+      <c r="K239" t="n">
         <v>713746</v>
-      </c>
-      <c r="K239" t="n">
-        <v>3519659962.5</v>
       </c>
       <c r="L239" t="n">
         <v>-0.004653044709690413</v>
@@ -10512,10 +10512,10 @@
         <v>2.378048780487794</v>
       </c>
       <c r="J240" t="n">
+        <v>19368</v>
+      </c>
+      <c r="K240" t="n">
         <v>961153</v>
-      </c>
-      <c r="K240" t="n">
-        <v>4781736175</v>
       </c>
       <c r="L240" t="n">
         <v>0.02378048780487796</v>
@@ -10554,10 +10554,10 @@
         <v>-4.705181655747464</v>
       </c>
       <c r="J241" t="n">
+        <v>19961</v>
+      </c>
+      <c r="K241" t="n">
         <v>978697</v>
-      </c>
-      <c r="K241" t="n">
-        <v>4807604338.25</v>
       </c>
       <c r="L241" t="n">
         <v>-0.04705181655747459</v>
@@ -10596,10 +10596,10 @@
         <v>4.562499999999995</v>
       </c>
       <c r="J242" t="n">
+        <v>26482</v>
+      </c>
+      <c r="K242" t="n">
         <v>1300405</v>
-      </c>
-      <c r="K242" t="n">
-        <v>6383363043.75</v>
       </c>
       <c r="L242" t="n">
         <v>0.04562500000000003</v>
@@ -10638,10 +10638,10 @@
         <v>-2.032277346084869</v>
       </c>
       <c r="J243" t="n">
+        <v>19030</v>
+      </c>
+      <c r="K243" t="n">
         <v>946653</v>
-      </c>
-      <c r="K243" t="n">
-        <v>4725928439.25</v>
       </c>
       <c r="L243" t="n">
         <v>-0.02032277346084865</v>
@@ -10680,10 +10680,10 @@
         <v>-1.565995525727076</v>
       </c>
       <c r="J244" t="n">
+        <v>12579</v>
+      </c>
+      <c r="K244" t="n">
         <v>611443</v>
-      </c>
-      <c r="K244" t="n">
-        <v>2968861486.5</v>
       </c>
       <c r="L244" t="n">
         <v>-0.01565995525727071</v>
@@ -10722,10 +10722,10 @@
         <v>-2.479338842975198</v>
       </c>
       <c r="J245" t="n">
+        <v>17112</v>
+      </c>
+      <c r="K245" t="n">
         <v>815364</v>
-      </c>
-      <c r="K245" t="n">
-        <v>3886840188</v>
       </c>
       <c r="L245" t="n">
         <v>-0.02479338842975198</v>
@@ -10764,10 +10764,10 @@
         <v>-1.207627118644068</v>
       </c>
       <c r="J246" t="n">
+        <v>13655</v>
+      </c>
+      <c r="K246" t="n">
         <v>639249</v>
-      </c>
-      <c r="K246" t="n">
-        <v>3004789924.5</v>
       </c>
       <c r="L246" t="n">
         <v>-0.01207627118644072</v>
@@ -10806,10 +10806,10 @@
         <v>0.9650439631138661</v>
       </c>
       <c r="J247" t="n">
+        <v>19676</v>
+      </c>
+      <c r="K247" t="n">
         <v>930264</v>
-      </c>
-      <c r="K247" t="n">
-        <v>4425265848</v>
       </c>
       <c r="L247" t="n">
         <v>0.009650439631138763</v>
@@ -10848,10 +10848,10 @@
         <v>-2.4214103653356</v>
       </c>
       <c r="J248" t="n">
+        <v>14787</v>
+      </c>
+      <c r="K248" t="n">
         <v>684211</v>
-      </c>
-      <c r="K248" t="n">
-        <v>3178331147.75</v>
       </c>
       <c r="L248" t="n">
         <v>-0.02421410365335597</v>
@@ -10890,10 +10890,10 @@
         <v>0.9577710056595665</v>
       </c>
       <c r="J249" t="n">
+        <v>13401</v>
+      </c>
+      <c r="K249" t="n">
         <v>621286</v>
-      </c>
-      <c r="K249" t="n">
-        <v>2866924247</v>
       </c>
       <c r="L249" t="n">
         <v>0.00957771005659569</v>
@@ -10932,10 +10932,10 @@
         <v>1.358344113842163</v>
       </c>
       <c r="J250" t="n">
+        <v>13351</v>
+      </c>
+      <c r="K250" t="n">
         <v>621576</v>
-      </c>
-      <c r="K250" t="n">
-        <v>2896544160</v>
       </c>
       <c r="L250" t="n">
         <v>0.01358344113842169</v>
@@ -10974,10 +10974,10 @@
         <v>-0.06381620931716898</v>
       </c>
       <c r="J251" t="n">
+        <v>10106</v>
+      </c>
+      <c r="K251" t="n">
         <v>473374</v>
-      </c>
-      <c r="K251" t="n">
-        <v>2214206885</v>
       </c>
       <c r="L251" t="n">
         <v>-0.0006381620931716903</v>
@@ -11016,10 +11016,10 @@
         <v>3.2141336739038</v>
       </c>
       <c r="J252" t="n">
+        <v>20963</v>
+      </c>
+      <c r="K252" t="n">
         <v>1002990</v>
-      </c>
-      <c r="K252" t="n">
-        <v>4794292200</v>
       </c>
       <c r="L252" t="n">
         <v>0.03214133673903796</v>
@@ -11058,10 +11058,10 @@
         <v>-1.257991338420292</v>
       </c>
       <c r="J253" t="n">
+        <v>13900</v>
+      </c>
+      <c r="K253" t="n">
         <v>669408</v>
-      </c>
-      <c r="K253" t="n">
-        <v>3225542448</v>
       </c>
       <c r="L253" t="n">
         <v>-0.01257991338420295</v>
@@ -11100,10 +11100,10 @@
         <v>-1.106934001670846</v>
       </c>
       <c r="J254" t="n">
+        <v>10594</v>
+      </c>
+      <c r="K254" t="n">
         <v>502935</v>
-      </c>
-      <c r="K254" t="n">
-        <v>2391204457.5</v>
       </c>
       <c r="L254" t="n">
         <v>-0.01106934001670845</v>
@@ -11142,10 +11142,10 @@
         <v>-0.7602956705385415</v>
       </c>
       <c r="J255" t="n">
+        <v>10984</v>
+      </c>
+      <c r="K255" t="n">
         <v>518239</v>
-      </c>
-      <c r="K255" t="n">
-        <v>2446088080</v>
       </c>
       <c r="L255" t="n">
         <v>-0.007602956705385466</v>
@@ -11184,10 +11184,10 @@
         <v>3.043200680995956</v>
       </c>
       <c r="J256" t="n">
+        <v>24860</v>
+      </c>
+      <c r="K256" t="n">
         <v>1185928</v>
-      </c>
-      <c r="K256" t="n">
-        <v>5678223264</v>
       </c>
       <c r="L256" t="n">
         <v>0.0304320068099595</v>
@@ -11226,10 +11226,10 @@
         <v>1.941346551011974</v>
       </c>
       <c r="J257" t="n">
+        <v>19400</v>
+      </c>
+      <c r="K257" t="n">
         <v>946321</v>
-      </c>
-      <c r="K257" t="n">
-        <v>4596044516.75</v>
       </c>
       <c r="L257" t="n">
         <v>0.01941346551011969</v>
@@ -11268,10 +11268,10 @@
         <v>-0.7698541329011397</v>
       </c>
       <c r="J258" t="n">
+        <v>21920</v>
+      </c>
+      <c r="K258" t="n">
         <v>1075827</v>
-      </c>
-      <c r="K258" t="n">
-        <v>5322116169</v>
       </c>
       <c r="L258" t="n">
         <v>-0.007698541329011377</v>
@@ -11310,10 +11310,10 @@
         <v>2.592895059207847</v>
       </c>
       <c r="J259" t="n">
+        <v>27387</v>
+      </c>
+      <c r="K259" t="n">
         <v>1358812</v>
-      </c>
-      <c r="K259" t="n">
-        <v>6777754256</v>
       </c>
       <c r="L259" t="n">
         <v>0.02592895059207856</v>
@@ -11352,10 +11352,10 @@
         <v>-0.4179104477611957</v>
       </c>
       <c r="J260" t="n">
+        <v>21049</v>
+      </c>
+      <c r="K260" t="n">
         <v>1051386</v>
-      </c>
-      <c r="K260" t="n">
-        <v>5240107824</v>
       </c>
       <c r="L260" t="n">
         <v>-0.004179104477611939</v>
@@ -11394,10 +11394,10 @@
         <v>-2.737809752198237</v>
       </c>
       <c r="J261" t="n">
+        <v>15124</v>
+      </c>
+      <c r="K261" t="n">
         <v>749617</v>
-      </c>
-      <c r="K261" t="n">
-        <v>3719599554</v>
       </c>
       <c r="L261" t="n">
         <v>-0.02737809752198239</v>
@@ -11436,10 +11436,10 @@
         <v>8.752825148962396</v>
       </c>
       <c r="J262" t="n">
+        <v>33894</v>
+      </c>
+      <c r="K262" t="n">
         <v>1727562</v>
-      </c>
-      <c r="K262" t="n">
-        <v>8796745704</v>
       </c>
       <c r="L262" t="n">
         <v>0.08752825148962406</v>
@@ -11478,10 +11478,10 @@
         <v>-1.681466087285095</v>
       </c>
       <c r="J263" t="n">
+        <v>21834</v>
+      </c>
+      <c r="K263" t="n">
         <v>1146413</v>
-      </c>
-      <c r="K263" t="n">
-        <v>6023253902</v>
       </c>
       <c r="L263" t="n">
         <v>-0.01681466087285099</v>
@@ -11520,10 +11520,10 @@
         <v>3.343581860107613</v>
       </c>
       <c r="J264" t="n">
+        <v>29781</v>
+      </c>
+      <c r="K264" t="n">
         <v>1569308</v>
-      </c>
-      <c r="K264" t="n">
-        <v>8226704863</v>
       </c>
       <c r="L264" t="n">
         <v>0.03343581860107614</v>
@@ -11562,10 +11562,10 @@
         <v>-0.5392339159538846</v>
       </c>
       <c r="J265" t="n">
+        <v>24611</v>
+      </c>
+      <c r="K265" t="n">
         <v>1320238</v>
-      </c>
-      <c r="K265" t="n">
-        <v>7123674188.5</v>
       </c>
       <c r="L265" t="n">
         <v>-0.00539233915953885</v>
@@ -11604,10 +11604,10 @@
         <v>1.794727986539542</v>
       </c>
       <c r="J266" t="n">
+        <v>20159</v>
+      </c>
+      <c r="K266" t="n">
         <v>1098671</v>
-      </c>
-      <c r="K266" t="n">
-        <v>5972100888.25</v>
       </c>
       <c r="L266" t="n">
         <v>0.01794727986539546</v>
@@ -11716,10 +11716,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>7956</v>
+      </c>
+      <c r="K2" t="n">
         <v>434450</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2376984562.5</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -11756,10 +11756,10 @@
         <v>0.7498171177761589</v>
       </c>
       <c r="J3" t="n">
+        <v>6718</v>
+      </c>
+      <c r="K3" t="n">
         <v>368593</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2025234238.5</v>
       </c>
       <c r="L3" t="n">
         <v>0.007498171177761526</v>
@@ -11798,10 +11798,10 @@
         <v>-2.559448175712477</v>
       </c>
       <c r="J4" t="n">
+        <v>9123</v>
+      </c>
+      <c r="K4" t="n">
         <v>495273</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2684751114.75</v>
       </c>
       <c r="L4" t="n">
         <v>-0.02559448175712475</v>
@@ -11840,10 +11840,10 @@
         <v>-0.149031296572277</v>
       </c>
       <c r="J5" t="n">
+        <v>6422</v>
+      </c>
+      <c r="K5" t="n">
         <v>344534</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1847219041</v>
       </c>
       <c r="L5" t="n">
         <v>-0.001490312965722773</v>
@@ -11882,10 +11882,10 @@
         <v>1.044776119402976</v>
       </c>
       <c r="J6" t="n">
+        <v>12169</v>
+      </c>
+      <c r="K6" t="n">
         <v>656906</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3565849994.5</v>
       </c>
       <c r="L6" t="n">
         <v>0.01044776119402968</v>
@@ -11924,10 +11924,10 @@
         <v>1.421713441654363</v>
       </c>
       <c r="J7" t="n">
+        <v>8812</v>
+      </c>
+      <c r="K7" t="n">
         <v>480735</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2630702103.75</v>
       </c>
       <c r="L7" t="n">
         <v>0.0142171344165436</v>
@@ -11966,10 +11966,10 @@
         <v>-0.7646095030038261</v>
       </c>
       <c r="J8" t="n">
+        <v>6911</v>
+      </c>
+      <c r="K8" t="n">
         <v>377736</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2070654318</v>
       </c>
       <c r="L8" t="n">
         <v>-0.007646095030038214</v>
@@ -12008,10 +12008,10 @@
         <v>2.036323610346725</v>
       </c>
       <c r="J9" t="n">
+        <v>8982</v>
+      </c>
+      <c r="K9" t="n">
         <v>493188</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2707848714</v>
       </c>
       <c r="L9" t="n">
         <v>0.02036323610346735</v>
@@ -12050,10 +12050,10 @@
         <v>-3.469974829198129</v>
       </c>
       <c r="J10" t="n">
+        <v>12094</v>
+      </c>
+      <c r="K10" t="n">
         <v>660238</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3604899480</v>
       </c>
       <c r="L10" t="n">
         <v>-0.0346997482919813</v>
@@ -12092,10 +12092,10 @@
         <v>-0.2421307506053184</v>
       </c>
       <c r="J11" t="n">
+        <v>7347</v>
+      </c>
+      <c r="K11" t="n">
         <v>392241</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2094076638.75</v>
       </c>
       <c r="L11" t="n">
         <v>-0.002421307506053183</v>
@@ -12134,10 +12134,10 @@
         <v>-3.584764749813297</v>
       </c>
       <c r="J12" t="n">
+        <v>13186</v>
+      </c>
+      <c r="K12" t="n">
         <v>695180</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3664467575</v>
       </c>
       <c r="L12" t="n">
         <v>-0.03584764749813296</v>
@@ -12176,10 +12176,10 @@
         <v>-0.05809450038729887</v>
       </c>
       <c r="J13" t="n">
+        <v>6480</v>
+      </c>
+      <c r="K13" t="n">
         <v>334095</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1722760867.5</v>
       </c>
       <c r="L13" t="n">
         <v>-0.0005809450038729569</v>
@@ -12218,10 +12218,10 @@
         <v>-0.4456500678163086</v>
       </c>
       <c r="J14" t="n">
+        <v>7245</v>
+      </c>
+      <c r="K14" t="n">
         <v>373167</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1924795386</v>
       </c>
       <c r="L14" t="n">
         <v>-0.004456500678163056</v>
@@ -12260,10 +12260,10 @@
         <v>0.3503308680420391</v>
       </c>
       <c r="J15" t="n">
+        <v>4667</v>
+      </c>
+      <c r="K15" t="n">
         <v>240608</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1243161384</v>
       </c>
       <c r="L15" t="n">
         <v>0.003503308680420369</v>
@@ -12302,10 +12302,10 @@
         <v>0.3878975950349025</v>
       </c>
       <c r="J16" t="n">
+        <v>6069</v>
+      </c>
+      <c r="K16" t="n">
         <v>313281</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1615120195.5</v>
       </c>
       <c r="L16" t="n">
         <v>0.003878975950349028</v>
@@ -12344,10 +12344,10 @@
         <v>0.3670788253477683</v>
       </c>
       <c r="J17" t="n">
+        <v>8687</v>
+      </c>
+      <c r="K17" t="n">
         <v>451035</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2341660961.25</v>
       </c>
       <c r="L17" t="n">
         <v>0.003670788253477664</v>
@@ -12386,10 +12386,10 @@
         <v>1.539942252165538</v>
       </c>
       <c r="J18" t="n">
+        <v>10248</v>
+      </c>
+      <c r="K18" t="n">
         <v>536482</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2798290112</v>
       </c>
       <c r="L18" t="n">
         <v>0.01539942252165538</v>
@@ -12428,10 +12428,10 @@
         <v>-1.649289099526062</v>
       </c>
       <c r="J19" t="n">
+        <v>7523</v>
+      </c>
+      <c r="K19" t="n">
         <v>392269</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2046957709.25</v>
       </c>
       <c r="L19" t="n">
         <v>-0.01649289099526063</v>
@@ -12470,10 +12470,10 @@
         <v>-0.2505782575173526</v>
       </c>
       <c r="J20" t="n">
+        <v>5563</v>
+      </c>
+      <c r="K20" t="n">
         <v>287765</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1487745050</v>
       </c>
       <c r="L20" t="n">
         <v>-0.002505782575173532</v>
@@ -12512,10 +12512,10 @@
         <v>-0.09661835748791722</v>
       </c>
       <c r="J21" t="n">
+        <v>8613</v>
+      </c>
+      <c r="K21" t="n">
         <v>445355</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2295693686.25</v>
       </c>
       <c r="L21" t="n">
         <v>-0.0009661835748792091</v>
@@ -12554,10 +12554,10 @@
         <v>1.083172147001925</v>
       </c>
       <c r="J22" t="n">
+        <v>7652</v>
+      </c>
+      <c r="K22" t="n">
         <v>397725</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2069064881.25</v>
       </c>
       <c r="L22" t="n">
         <v>0.01083172147001932</v>
@@ -12596,10 +12596,10 @@
         <v>-0.4018369690011497</v>
       </c>
       <c r="J23" t="n">
+        <v>6249</v>
+      </c>
+      <c r="K23" t="n">
         <v>325712</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1705020892</v>
       </c>
       <c r="L23" t="n">
         <v>-0.004018369690011458</v>
@@ -12638,10 +12638,10 @@
         <v>0.4226705091258521</v>
       </c>
       <c r="J24" t="n">
+        <v>5630</v>
+      </c>
+      <c r="K24" t="n">
         <v>293678</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1529475024</v>
       </c>
       <c r="L24" t="n">
         <v>0.004226705091258554</v>
@@ -12680,10 +12680,10 @@
         <v>1.511383202601873</v>
       </c>
       <c r="J25" t="n">
+        <v>9063</v>
+      </c>
+      <c r="K25" t="n">
         <v>477923</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2526539939.5</v>
       </c>
       <c r="L25" t="n">
         <v>0.01511383202601868</v>
@@ -12722,10 +12722,10 @@
         <v>-1.149641914813418</v>
       </c>
       <c r="J26" t="n">
+        <v>5422</v>
+      </c>
+      <c r="K26" t="n">
         <v>286388</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1513417386</v>
       </c>
       <c r="L26" t="n">
         <v>-0.01149641914813415</v>
@@ -12764,10 +12764,10 @@
         <v>1.429933269780743</v>
       </c>
       <c r="J27" t="n">
+        <v>6798</v>
+      </c>
+      <c r="K27" t="n">
         <v>359263</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1899423481</v>
       </c>
       <c r="L27" t="n">
         <v>0.01429933269780737</v>
@@ -12806,10 +12806,10 @@
         <v>7.124060150375938</v>
       </c>
       <c r="J28" t="n">
+        <v>21022</v>
+      </c>
+      <c r="K28" t="n">
         <v>1158212</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6391882475</v>
       </c>
       <c r="L28" t="n">
         <v>0.07124060150375944</v>
@@ -12848,10 +12848,10 @@
         <v>0.7194244604316486</v>
       </c>
       <c r="J29" t="n">
+        <v>15809</v>
+      </c>
+      <c r="K29" t="n">
         <v>903716</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5169707378</v>
       </c>
       <c r="L29" t="n">
         <v>0.007194244604316502</v>
@@ -12890,10 +12890,10 @@
         <v>-1.219512195121944</v>
       </c>
       <c r="J30" t="n">
+        <v>11554</v>
+      </c>
+      <c r="K30" t="n">
         <v>658632</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3764246538</v>
       </c>
       <c r="L30" t="n">
         <v>-0.01219512195121941</v>
@@ -12932,10 +12932,10 @@
         <v>0.5467372134038715</v>
       </c>
       <c r="J31" t="n">
+        <v>8344</v>
+      </c>
+      <c r="K31" t="n">
         <v>473758</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2697696491.5</v>
       </c>
       <c r="L31" t="n">
         <v>0.005467372134038806</v>
@@ -12974,10 +12974,10 @@
         <v>0.0175407823189004</v>
       </c>
       <c r="J32" t="n">
+        <v>7661</v>
+      </c>
+      <c r="K32" t="n">
         <v>436928</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2487431104</v>
       </c>
       <c r="L32" t="n">
         <v>0.0001754078231890333</v>
@@ -13016,10 +13016,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>6957</v>
+      </c>
+      <c r="K33" t="n">
         <v>398191</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2289697797.75</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -13058,10 +13058,10 @@
         <v>0.8944230094703578</v>
       </c>
       <c r="J34" t="n">
+        <v>7776</v>
+      </c>
+      <c r="K34" t="n">
         <v>444146</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2537961280.5</v>
       </c>
       <c r="L34" t="n">
         <v>0.008944230094703576</v>
@@ -13100,10 +13100,10 @@
         <v>1.790370241613073</v>
       </c>
       <c r="J35" t="n">
+        <v>11341</v>
+      </c>
+      <c r="K35" t="n">
         <v>660986</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3865611374.5</v>
       </c>
       <c r="L35" t="n">
         <v>0.01790370241613082</v>
@@ -13142,10 +13142,10 @@
         <v>-1.297814207650282</v>
       </c>
       <c r="J36" t="n">
+        <v>8776</v>
+      </c>
+      <c r="K36" t="n">
         <v>509442</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2957056089</v>
       </c>
       <c r="L36" t="n">
         <v>-0.01297814207650283</v>
@@ -13184,10 +13184,10 @@
         <v>-1.020761245674734</v>
       </c>
       <c r="J37" t="n">
+        <v>8270</v>
+      </c>
+      <c r="K37" t="n">
         <v>475570</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2742374405</v>
       </c>
       <c r="L37" t="n">
         <v>-0.01020761245674739</v>
@@ -13226,10 +13226,10 @@
         <v>-0.48942492571229</v>
       </c>
       <c r="J38" t="n">
+        <v>7466</v>
+      </c>
+      <c r="K38" t="n">
         <v>425295</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2429285040</v>
       </c>
       <c r="L38" t="n">
         <v>-0.004894249257122896</v>
@@ -13268,10 +13268,10 @@
         <v>0.6499209555594545</v>
       </c>
       <c r="J39" t="n">
+        <v>8134</v>
+      </c>
+      <c r="K39" t="n">
         <v>465834</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2667714859.5</v>
       </c>
       <c r="L39" t="n">
         <v>0.006499209555594465</v>
@@ -13310,10 +13310,10 @@
         <v>-1.919720767888297</v>
       </c>
       <c r="J40" t="n">
+        <v>8906</v>
+      </c>
+      <c r="K40" t="n">
         <v>505394</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2868110950</v>
       </c>
       <c r="L40" t="n">
         <v>-0.019197207678883</v>
@@ -13352,10 +13352,10 @@
         <v>10.0355871886121</v>
       </c>
       <c r="J41" t="n">
+        <v>26780</v>
+      </c>
+      <c r="K41" t="n">
         <v>1630096</v>
-      </c>
-      <c r="K41" t="n">
-        <v>9904463296</v>
       </c>
       <c r="L41" t="n">
         <v>0.1003558718861211</v>
@@ -13394,10 +13394,10 @@
         <v>2.84605433376455</v>
       </c>
       <c r="J42" t="n">
+        <v>26626</v>
+      </c>
+      <c r="K42" t="n">
         <v>1682769</v>
-      </c>
-      <c r="K42" t="n">
-        <v>10667072691</v>
       </c>
       <c r="L42" t="n">
         <v>0.02846054333764547</v>
@@ -13436,10 +13436,10 @@
         <v>-0.3301886792452843</v>
       </c>
       <c r="J43" t="n">
+        <v>15446</v>
+      </c>
+      <c r="K43" t="n">
         <v>980849</v>
-      </c>
-      <c r="K43" t="n">
-        <v>6227900725.5</v>
       </c>
       <c r="L43" t="n">
         <v>-0.003301886792452802</v>
@@ -13478,10 +13478,10 @@
         <v>-1.088499763369613</v>
       </c>
       <c r="J44" t="n">
+        <v>11788</v>
+      </c>
+      <c r="K44" t="n">
         <v>742039</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4679483443.75</v>
       </c>
       <c r="L44" t="n">
         <v>-0.0108849976336961</v>
@@ -13520,10 +13520,10 @@
         <v>-2.53588516746412</v>
       </c>
       <c r="J45" t="n">
+        <v>11874</v>
+      </c>
+      <c r="K45" t="n">
         <v>734655</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4548983760</v>
       </c>
       <c r="L45" t="n">
         <v>-0.02535885167464125</v>
@@ -13562,10 +13562,10 @@
         <v>1.129111438389785</v>
       </c>
       <c r="J46" t="n">
+        <v>11287</v>
+      </c>
+      <c r="K46" t="n">
         <v>689613</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4204053251.25</v>
       </c>
       <c r="L46" t="n">
         <v>0.01129111438389785</v>
@@ -13604,10 +13604,10 @@
         <v>0.4854368932038904</v>
       </c>
       <c r="J47" t="n">
+        <v>8732</v>
+      </c>
+      <c r="K47" t="n">
         <v>541443</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3351938252.25</v>
       </c>
       <c r="L47" t="n">
         <v>0.004854368932038833</v>
@@ -13646,10 +13646,10 @@
         <v>-1.159420289855071</v>
       </c>
       <c r="J48" t="n">
+        <v>9281</v>
+      </c>
+      <c r="K48" t="n">
         <v>572479</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3533626627.5</v>
       </c>
       <c r="L48" t="n">
         <v>-0.01159420289855073</v>
@@ -13688,10 +13688,10 @@
         <v>-1.254480286738356</v>
       </c>
       <c r="J49" t="n">
+        <v>8298</v>
+      </c>
+      <c r="K49" t="n">
         <v>504764</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3079817546</v>
       </c>
       <c r="L49" t="n">
         <v>-0.01254480286738358</v>
@@ -13730,10 +13730,10 @@
         <v>0.296980696254743</v>
       </c>
       <c r="J50" t="n">
+        <v>5985</v>
+      </c>
+      <c r="K50" t="n">
         <v>362971</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2196156035.5</v>
       </c>
       <c r="L50" t="n">
         <v>0.00296980696254745</v>
@@ -13772,10 +13772,10 @@
         <v>0.1316005922026621</v>
       </c>
       <c r="J51" t="n">
+        <v>6999</v>
+      </c>
+      <c r="K51" t="n">
         <v>425752</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2590275168</v>
       </c>
       <c r="L51" t="n">
         <v>0.00131600592202652</v>
@@ -13814,10 +13814,10 @@
         <v>-0.3614259898143566</v>
       </c>
       <c r="J52" t="n">
+        <v>6436</v>
+      </c>
+      <c r="K52" t="n">
         <v>391835</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2381181295</v>
       </c>
       <c r="L52" t="n">
         <v>-0.003614259898143568</v>
@@ -13856,10 +13856,10 @@
         <v>2.901896125309148</v>
       </c>
       <c r="J53" t="n">
+        <v>13250</v>
+      </c>
+      <c r="K53" t="n">
         <v>815296</v>
-      </c>
-      <c r="K53" t="n">
-        <v>5034860448</v>
       </c>
       <c r="L53" t="n">
         <v>0.02901896125309156</v>
@@ -13898,10 +13898,10 @@
         <v>0.3364845377343388</v>
       </c>
       <c r="J54" t="n">
+        <v>9121</v>
+      </c>
+      <c r="K54" t="n">
         <v>571266</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3582266269.5</v>
       </c>
       <c r="L54" t="n">
         <v>0.003364845377343384</v>
@@ -13940,10 +13940,10 @@
         <v>0.9262216544235156</v>
       </c>
       <c r="J55" t="n">
+        <v>9789</v>
+      </c>
+      <c r="K55" t="n">
         <v>614933</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3873616700.25</v>
       </c>
       <c r="L55" t="n">
         <v>0.009262216544235091</v>
@@ -13982,10 +13982,10 @@
         <v>-0.5063291139240511</v>
       </c>
       <c r="J56" t="n">
+        <v>11562</v>
+      </c>
+      <c r="K56" t="n">
         <v>728858</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4599822838</v>
       </c>
       <c r="L56" t="n">
         <v>-0.005063291139240533</v>
@@ -14024,10 +14024,10 @@
         <v>-2.21055979643766</v>
       </c>
       <c r="J57" t="n">
+        <v>16003</v>
+      </c>
+      <c r="K57" t="n">
         <v>997700</v>
-      </c>
-      <c r="K57" t="n">
-        <v>6268549100</v>
       </c>
       <c r="L57" t="n">
         <v>-0.02210559796437661</v>
@@ -14066,10 +14066,10 @@
         <v>1.886485607415834</v>
       </c>
       <c r="J58" t="n">
+        <v>10481</v>
+      </c>
+      <c r="K58" t="n">
         <v>650424</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4029214074</v>
       </c>
       <c r="L58" t="n">
         <v>0.01886485607415844</v>
@@ -14108,10 +14108,10 @@
         <v>1.819632881085396</v>
       </c>
       <c r="J59" t="n">
+        <v>13461</v>
+      </c>
+      <c r="K59" t="n">
         <v>858629</v>
-      </c>
-      <c r="K59" t="n">
-        <v>5483419451.25</v>
       </c>
       <c r="L59" t="n">
         <v>0.01819632881085398</v>
@@ -14150,10 +14150,10 @@
         <v>1.551967393008312</v>
       </c>
       <c r="J60" t="n">
+        <v>9865</v>
+      </c>
+      <c r="K60" t="n">
         <v>637719</v>
-      </c>
-      <c r="K60" t="n">
-        <v>4112012112</v>
       </c>
       <c r="L60" t="n">
         <v>0.01551967393008313</v>
@@ -14192,10 +14192,10 @@
         <v>1.975918493362151</v>
       </c>
       <c r="J61" t="n">
+        <v>12981</v>
+      </c>
+      <c r="K61" t="n">
         <v>849234</v>
-      </c>
-      <c r="K61" t="n">
-        <v>5545710328.5</v>
       </c>
       <c r="L61" t="n">
         <v>0.01975918493362161</v>
@@ -14234,10 +14234,10 @@
         <v>-1.453224341507732</v>
       </c>
       <c r="J62" t="n">
+        <v>8774</v>
+      </c>
+      <c r="K62" t="n">
         <v>575129</v>
-      </c>
-      <c r="K62" t="n">
-        <v>3765657127.5</v>
       </c>
       <c r="L62" t="n">
         <v>-0.01453224341507731</v>
@@ -14276,10 +14276,10 @@
         <v>-3.456221198156671</v>
       </c>
       <c r="J63" t="n">
+        <v>13100</v>
+      </c>
+      <c r="K63" t="n">
         <v>836169</v>
-      </c>
-      <c r="K63" t="n">
-        <v>5351690642.25</v>
       </c>
       <c r="L63" t="n">
         <v>-0.03456221198156673</v>
@@ -14318,10 +14318,10 @@
         <v>-0.03182179793158811</v>
       </c>
       <c r="J64" t="n">
+        <v>11402</v>
+      </c>
+      <c r="K64" t="n">
         <v>715902</v>
-      </c>
-      <c r="K64" t="n">
-        <v>4470986965.5</v>
       </c>
       <c r="L64" t="n">
         <v>-0.0003182179793158602</v>
@@ -14360,10 +14360,10 @@
         <v>5.093108387712881</v>
       </c>
       <c r="J65" t="n">
+        <v>15881</v>
+      </c>
+      <c r="K65" t="n">
         <v>1023186</v>
-      </c>
-      <c r="K65" t="n">
-        <v>6608758374</v>
       </c>
       <c r="L65" t="n">
         <v>0.05093108387712886</v>
@@ -14402,10 +14402,10 @@
         <v>3.21066182038468</v>
       </c>
       <c r="J66" t="n">
+        <v>12984</v>
+      </c>
+      <c r="K66" t="n">
         <v>872181</v>
-      </c>
-      <c r="K66" t="n">
-        <v>5859966093.75</v>
       </c>
       <c r="L66" t="n">
         <v>0.03210661820384675</v>
@@ -14444,10 +14444,10 @@
         <v>0.7630227439471694</v>
       </c>
       <c r="J67" t="n">
+        <v>15687</v>
+      </c>
+      <c r="K67" t="n">
         <v>1084490</v>
-      </c>
-      <c r="K67" t="n">
-        <v>7494910390</v>
       </c>
       <c r="L67" t="n">
         <v>0.007630227439471726</v>
@@ -14486,10 +14486,10 @@
         <v>4.528906363768749</v>
       </c>
       <c r="J68" t="n">
+        <v>16090</v>
+      </c>
+      <c r="K68" t="n">
         <v>1129369</v>
-      </c>
-      <c r="K68" t="n">
-        <v>7967698295</v>
       </c>
       <c r="L68" t="n">
         <v>0.04528906363768748</v>
@@ -14528,10 +14528,10 @@
         <v>-4.639175257731956</v>
       </c>
       <c r="J69" t="n">
+        <v>15810</v>
+      </c>
+      <c r="K69" t="n">
         <v>1102894</v>
-      </c>
-      <c r="K69" t="n">
-        <v>7670627770</v>
       </c>
       <c r="L69" t="n">
         <v>-0.04639175257731953</v>
@@ -14570,10 +14570,10 @@
         <v>5.580715850986111</v>
       </c>
       <c r="J70" t="n">
+        <v>13277</v>
+      </c>
+      <c r="K70" t="n">
         <v>936479</v>
-      </c>
-      <c r="K70" t="n">
-        <v>6617394733.75</v>
       </c>
       <c r="L70" t="n">
         <v>0.05580715850986118</v>
@@ -14612,10 +14612,10 @@
         <v>-0.2213920022139153</v>
       </c>
       <c r="J71" t="n">
+        <v>10327</v>
+      </c>
+      <c r="K71" t="n">
         <v>748209</v>
-      </c>
-      <c r="K71" t="n">
-        <v>5424889354.5</v>
       </c>
       <c r="L71" t="n">
         <v>-0.00221392002213916</v>
@@ -14654,10 +14654,10 @@
         <v>-1.691859658854526</v>
       </c>
       <c r="J72" t="n">
+        <v>10747</v>
+      </c>
+      <c r="K72" t="n">
         <v>767670</v>
-      </c>
-      <c r="K72" t="n">
-        <v>5507648415</v>
       </c>
       <c r="L72" t="n">
         <v>-0.01691859658854522</v>
@@ -14696,10 +14696,10 @@
         <v>-1.0861898716321</v>
       </c>
       <c r="J73" t="n">
+        <v>6653</v>
+      </c>
+      <c r="K73" t="n">
         <v>468204</v>
-      </c>
-      <c r="K73" t="n">
-        <v>3303296271</v>
       </c>
       <c r="L73" t="n">
         <v>-0.01086189871632104</v>
@@ -14738,10 +14738,10 @@
         <v>-2.895037079292643</v>
       </c>
       <c r="J74" t="n">
+        <v>28889</v>
+      </c>
+      <c r="K74" t="n">
         <v>1942359</v>
-      </c>
-      <c r="K74" t="n">
-        <v>12942909196.5</v>
       </c>
       <c r="L74" t="n">
         <v>-0.02895037079292639</v>
@@ -14780,10 +14780,10 @@
         <v>1.057423997650167</v>
       </c>
       <c r="J75" t="n">
+        <v>12144</v>
+      </c>
+      <c r="K75" t="n">
         <v>831215</v>
-      </c>
-      <c r="K75" t="n">
-        <v>5690913497.5</v>
       </c>
       <c r="L75" t="n">
         <v>0.01057423997650164</v>
@@ -14822,10 +14822,10 @@
         <v>0.1307949425955579</v>
       </c>
       <c r="J76" t="n">
+        <v>8897</v>
+      </c>
+      <c r="K76" t="n">
         <v>611882</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4208218455</v>
       </c>
       <c r="L76" t="n">
         <v>0.001307949425955579</v>
@@ -14864,10 +14864,10 @@
         <v>0.07256894049346467</v>
       </c>
       <c r="J77" t="n">
+        <v>6305</v>
+      </c>
+      <c r="K77" t="n">
         <v>434582</v>
-      </c>
-      <c r="K77" t="n">
-        <v>2989163641.5</v>
       </c>
       <c r="L77" t="n">
         <v>0.0007256894049345597</v>
@@ -14906,10 +14906,10 @@
         <v>1.421319796954321</v>
       </c>
       <c r="J78" t="n">
+        <v>8430</v>
+      </c>
+      <c r="K78" t="n">
         <v>586034</v>
-      </c>
-      <c r="K78" t="n">
-        <v>4083631420.5</v>
       </c>
       <c r="L78" t="n">
         <v>0.01421319796954323</v>
@@ -14948,10 +14948,10 @@
         <v>1.372801372801364</v>
       </c>
       <c r="J79" t="n">
+        <v>12257</v>
+      </c>
+      <c r="K79" t="n">
         <v>865639</v>
-      </c>
-      <c r="K79" t="n">
-        <v>6143223573.25</v>
       </c>
       <c r="L79" t="n">
         <v>0.01372801372801358</v>
@@ -14990,10 +14990,10 @@
         <v>-2.031316123571727</v>
       </c>
       <c r="J80" t="n">
+        <v>7473</v>
+      </c>
+      <c r="K80" t="n">
         <v>524392</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3679658664</v>
       </c>
       <c r="L80" t="n">
         <v>-0.02031316123571725</v>
@@ -15032,10 +15032,10 @@
         <v>2.015838732901356</v>
       </c>
       <c r="J81" t="n">
+        <v>8170</v>
+      </c>
+      <c r="K81" t="n">
         <v>576542</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4091142032</v>
       </c>
       <c r="L81" t="n">
         <v>0.02015838732901365</v>
@@ -15074,10 +15074,10 @@
         <v>-1.905434015525751</v>
       </c>
       <c r="J82" t="n">
+        <v>8002</v>
+      </c>
+      <c r="K82" t="n">
         <v>561330</v>
-      </c>
-      <c r="K82" t="n">
-        <v>3923556367.5</v>
       </c>
       <c r="L82" t="n">
         <v>-0.01905434015525753</v>
@@ -15116,10 +15116,10 @@
         <v>0.5899280575539519</v>
       </c>
       <c r="J83" t="n">
+        <v>5671</v>
+      </c>
+      <c r="K83" t="n">
         <v>395302</v>
-      </c>
-      <c r="K83" t="n">
-        <v>2754167859.5</v>
       </c>
       <c r="L83" t="n">
         <v>0.005899280575539567</v>
@@ -15158,10 +15158,10 @@
         <v>3.089686740094402</v>
       </c>
       <c r="J84" t="n">
+        <v>10245</v>
+      </c>
+      <c r="K84" t="n">
         <v>739039</v>
-      </c>
-      <c r="K84" t="n">
-        <v>5330318787.5</v>
       </c>
       <c r="L84" t="n">
         <v>0.03089686740094399</v>
@@ -15200,10 +15200,10 @@
         <v>-3.038712362980433</v>
       </c>
       <c r="J85" t="n">
+        <v>9952</v>
+      </c>
+      <c r="K85" t="n">
         <v>699045</v>
-      </c>
-      <c r="K85" t="n">
-        <v>4905198765</v>
       </c>
       <c r="L85" t="n">
         <v>-0.03038712362980434</v>
@@ -15242,10 +15242,10 @@
         <v>-1.259301659988545</v>
       </c>
       <c r="J86" t="n">
+        <v>9351</v>
+      </c>
+      <c r="K86" t="n">
         <v>647991</v>
-      </c>
-      <c r="K86" t="n">
-        <v>4466925958.5</v>
       </c>
       <c r="L86" t="n">
         <v>-0.01259301659988543</v>
@@ -15284,10 +15284,10 @@
         <v>3.405797101449267</v>
       </c>
       <c r="J87" t="n">
+        <v>8269</v>
+      </c>
+      <c r="K87" t="n">
         <v>579451</v>
-      </c>
-      <c r="K87" t="n">
-        <v>4058040215.75</v>
       </c>
       <c r="L87" t="n">
         <v>0.03405797101449259</v>
@@ -15326,10 +15326,10 @@
         <v>-0.5606166783461689</v>
       </c>
       <c r="J88" t="n">
+        <v>8331</v>
+      </c>
+      <c r="K88" t="n">
         <v>592793</v>
-      </c>
-      <c r="K88" t="n">
-        <v>4189268131</v>
       </c>
       <c r="L88" t="n">
         <v>-0.005606166783461708</v>
@@ -15368,10 +15368,10 @@
         <v>-4.157857646229743</v>
       </c>
       <c r="J89" t="n">
+        <v>10220</v>
+      </c>
+      <c r="K89" t="n">
         <v>706101</v>
-      </c>
-      <c r="K89" t="n">
-        <v>4881099687.75</v>
       </c>
       <c r="L89" t="n">
         <v>-0.04157857646229746</v>
@@ -15410,10 +15410,10 @@
         <v>-1.794117647058822</v>
       </c>
       <c r="J90" t="n">
+        <v>8030</v>
+      </c>
+      <c r="K90" t="n">
         <v>532287</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3538510904.25</v>
       </c>
       <c r="L90" t="n">
         <v>-0.01794117647058824</v>
@@ -15452,10 +15452,10 @@
         <v>-4.058101227912561</v>
       </c>
       <c r="J91" t="n">
+        <v>10693</v>
+      </c>
+      <c r="K91" t="n">
         <v>702947</v>
-      </c>
-      <c r="K91" t="n">
-        <v>4612035267</v>
       </c>
       <c r="L91" t="n">
         <v>-0.04058101227912558</v>
@@ -15494,10 +15494,10 @@
         <v>3.324488840330903</v>
       </c>
       <c r="J92" t="n">
+        <v>7853</v>
+      </c>
+      <c r="K92" t="n">
         <v>511232</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3321729920</v>
       </c>
       <c r="L92" t="n">
         <v>0.03324488840330897</v>
@@ -15536,10 +15536,10 @@
         <v>0.6646525679758274</v>
       </c>
       <c r="J93" t="n">
+        <v>6930</v>
+      </c>
+      <c r="K93" t="n">
         <v>460378</v>
-      </c>
-      <c r="K93" t="n">
-        <v>3069455220.5</v>
       </c>
       <c r="L93" t="n">
         <v>0.006646525679758319</v>
@@ -15578,10 +15578,10 @@
         <v>-2.611044417767099</v>
       </c>
       <c r="J94" t="n">
+        <v>5314</v>
+      </c>
+      <c r="K94" t="n">
         <v>349507</v>
-      </c>
-      <c r="K94" t="n">
-        <v>2302814246.25</v>
       </c>
       <c r="L94" t="n">
         <v>-0.02611044417767094</v>
@@ -15620,10 +15620,10 @@
         <v>0.04622496147920051</v>
       </c>
       <c r="J95" t="n">
+        <v>4999</v>
+      </c>
+      <c r="K95" t="n">
         <v>326717</v>
-      </c>
-      <c r="K95" t="n">
-        <v>2137219255.5</v>
       </c>
       <c r="L95" t="n">
         <v>0.0004622496147919097</v>
@@ -15662,10 +15662,10 @@
         <v>1.339904512551964</v>
       </c>
       <c r="J96" t="n">
+        <v>5638</v>
+      </c>
+      <c r="K96" t="n">
         <v>369560</v>
-      </c>
-      <c r="K96" t="n">
-        <v>2424498380</v>
       </c>
       <c r="L96" t="n">
         <v>0.0133990451255197</v>
@@ -15704,10 +15704,10 @@
         <v>-1.124620060790266</v>
       </c>
       <c r="J97" t="n">
+        <v>6072</v>
+      </c>
+      <c r="K97" t="n">
         <v>398048</v>
-      </c>
-      <c r="K97" t="n">
-        <v>2612289512</v>
       </c>
       <c r="L97" t="n">
         <v>-0.01124620060790271</v>
@@ -15746,10 +15746,10 @@
         <v>-0.1844451275745536</v>
       </c>
       <c r="J98" t="n">
+        <v>5284</v>
+      </c>
+      <c r="K98" t="n">
         <v>342785</v>
-      </c>
-      <c r="K98" t="n">
-        <v>2217818950</v>
       </c>
       <c r="L98" t="n">
         <v>-0.001844451275745507</v>
@@ -15788,10 +15788,10 @@
         <v>0.5543578688019702</v>
       </c>
       <c r="J99" t="n">
+        <v>5719</v>
+      </c>
+      <c r="K99" t="n">
         <v>372753</v>
-      </c>
-      <c r="K99" t="n">
-        <v>2435288537.25</v>
       </c>
       <c r="L99" t="n">
         <v>0.005543578688019801</v>
@@ -15830,10 +15830,10 @@
         <v>2.312404287901999</v>
       </c>
       <c r="J100" t="n">
+        <v>7644</v>
+      </c>
+      <c r="K100" t="n">
         <v>508925</v>
-      </c>
-      <c r="K100" t="n">
-        <v>3398601150</v>
       </c>
       <c r="L100" t="n">
         <v>0.02312404287902003</v>
@@ -15872,10 +15872,10 @@
         <v>-5.074090704984284</v>
       </c>
       <c r="J101" t="n">
+        <v>16850</v>
+      </c>
+      <c r="K101" t="n">
         <v>1082090</v>
-      </c>
-      <c r="K101" t="n">
-        <v>6952428250</v>
       </c>
       <c r="L101" t="n">
         <v>-0.0507409070498428</v>
@@ -15914,10 +15914,10 @@
         <v>0.6307158625039397</v>
       </c>
       <c r="J102" t="n">
+        <v>8838</v>
+      </c>
+      <c r="K102" t="n">
         <v>562175</v>
-      </c>
-      <c r="K102" t="n">
-        <v>3569951793.75</v>
       </c>
       <c r="L102" t="n">
         <v>0.006307158625039389</v>
@@ -15956,10 +15956,10 @@
         <v>-1.786273895330618</v>
       </c>
       <c r="J103" t="n">
+        <v>9624</v>
+      </c>
+      <c r="K103" t="n">
         <v>608740</v>
-      </c>
-      <c r="K103" t="n">
-        <v>3850128315</v>
       </c>
       <c r="L103" t="n">
         <v>-0.01786273895330615</v>
@@ -15998,10 +15998,10 @@
         <v>2.026164645820043</v>
       </c>
       <c r="J104" t="n">
+        <v>13171</v>
+      </c>
+      <c r="K104" t="n">
         <v>837064</v>
-      </c>
-      <c r="K104" t="n">
-        <v>5344653640</v>
       </c>
       <c r="L104" t="n">
         <v>0.02026164645820039</v>
@@ -16040,10 +16040,10 @@
         <v>-1.172791243158718</v>
       </c>
       <c r="J105" t="n">
+        <v>7195</v>
+      </c>
+      <c r="K105" t="n">
         <v>460306</v>
-      </c>
-      <c r="K105" t="n">
-        <v>2938708580.5</v>
       </c>
       <c r="L105" t="n">
         <v>-0.01172791243158722</v>
@@ -16082,10 +16082,10 @@
         <v>-2.34177215189874</v>
       </c>
       <c r="J106" t="n">
+        <v>8254</v>
+      </c>
+      <c r="K106" t="n">
         <v>515610</v>
-      </c>
-      <c r="K106" t="n">
-        <v>3216632985</v>
       </c>
       <c r="L106" t="n">
         <v>-0.02341772151898736</v>
@@ -16124,10 +16124,10 @@
         <v>0.06480881399870245</v>
       </c>
       <c r="J107" t="n">
+        <v>5443</v>
+      </c>
+      <c r="K107" t="n">
         <v>334381</v>
-      </c>
-      <c r="K107" t="n">
-        <v>2057864269.25</v>
       </c>
       <c r="L107" t="n">
         <v>0.0006480881399870686</v>
@@ -16166,10 +16166,10 @@
         <v>0.7448186528497424</v>
       </c>
       <c r="J108" t="n">
+        <v>4074</v>
+      </c>
+      <c r="K108" t="n">
         <v>252524</v>
-      </c>
-      <c r="K108" t="n">
-        <v>1562744774</v>
       </c>
       <c r="L108" t="n">
         <v>0.007448186528497436</v>
@@ -16208,10 +16208,10 @@
         <v>-1.350048216007709</v>
       </c>
       <c r="J109" t="n">
+        <v>4394</v>
+      </c>
+      <c r="K109" t="n">
         <v>270654</v>
-      </c>
-      <c r="K109" t="n">
-        <v>1669732189.5</v>
       </c>
       <c r="L109" t="n">
         <v>-0.01350048216007704</v>
@@ -16250,10 +16250,10 @@
         <v>0.4072987943955685</v>
       </c>
       <c r="J110" t="n">
+        <v>6443</v>
+      </c>
+      <c r="K110" t="n">
         <v>396248</v>
-      </c>
-      <c r="K110" t="n">
-        <v>2431873038</v>
       </c>
       <c r="L110" t="n">
         <v>0.004072987943955608</v>
@@ -16292,10 +16292,10 @@
         <v>-1.249391530098983</v>
       </c>
       <c r="J111" t="n">
+        <v>4488</v>
+      </c>
+      <c r="K111" t="n">
         <v>275160</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1688175390</v>
       </c>
       <c r="L111" t="n">
         <v>-0.01249391530098987</v>
@@ -16334,10 +16334,10 @@
         <v>1.70883996056523</v>
       </c>
       <c r="J112" t="n">
+        <v>8376</v>
+      </c>
+      <c r="K112" t="n">
         <v>514268</v>
-      </c>
-      <c r="K112" t="n">
-        <v>3167119478</v>
       </c>
       <c r="L112" t="n">
         <v>0.01708839960565234</v>
@@ -16376,10 +16376,10 @@
         <v>2.35864297253635</v>
       </c>
       <c r="J113" t="n">
+        <v>8078</v>
+      </c>
+      <c r="K113" t="n">
         <v>508318</v>
-      </c>
-      <c r="K113" t="n">
-        <v>3195668186.5</v>
       </c>
       <c r="L113" t="n">
         <v>0.0235864297253634</v>
@@ -16418,10 +16418,10 @@
         <v>-1.041666666666661</v>
       </c>
       <c r="J114" t="n">
+        <v>5074</v>
+      </c>
+      <c r="K114" t="n">
         <v>319504</v>
-      </c>
-      <c r="K114" t="n">
-        <v>2014552596</v>
       </c>
       <c r="L114" t="n">
         <v>-0.01041666666666663</v>
@@ -16460,10 +16460,10 @@
         <v>-1.754385964912283</v>
       </c>
       <c r="J115" t="n">
+        <v>5075</v>
+      </c>
+      <c r="K115" t="n">
         <v>315385</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1958146618.75</v>
       </c>
       <c r="L115" t="n">
         <v>-0.01754385964912286</v>
@@ -16502,10 +16502,10 @@
         <v>-0.03246753246753754</v>
       </c>
       <c r="J116" t="n">
+        <v>3563</v>
+      </c>
+      <c r="K116" t="n">
         <v>219101</v>
-      </c>
-      <c r="K116" t="n">
-        <v>1352729574</v>
       </c>
       <c r="L116" t="n">
         <v>-0.0003246753246753942</v>
@@ -16544,10 +16544,10 @@
         <v>-1.088015589477106</v>
       </c>
       <c r="J117" t="n">
+        <v>3456</v>
+      </c>
+      <c r="K117" t="n">
         <v>211162</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1291308420.5</v>
       </c>
       <c r="L117" t="n">
         <v>-0.01088015589477109</v>
@@ -16586,10 +16586,10 @@
         <v>-0.7880479395829862</v>
       </c>
       <c r="J118" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K118" t="n">
         <v>253480</v>
-      </c>
-      <c r="K118" t="n">
-        <v>1541475250</v>
       </c>
       <c r="L118" t="n">
         <v>-0.007880479395829809</v>
@@ -16628,10 +16628,10 @@
         <v>-1.869932152904191</v>
       </c>
       <c r="J119" t="n">
+        <v>7491</v>
+      </c>
+      <c r="K119" t="n">
         <v>447335</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2677747310</v>
       </c>
       <c r="L119" t="n">
         <v>-0.01869932152904186</v>
@@ -16670,10 +16670,10 @@
         <v>1.956155143338961</v>
       </c>
       <c r="J120" t="n">
+        <v>5719</v>
+      </c>
+      <c r="K120" t="n">
         <v>343973</v>
-      </c>
-      <c r="K120" t="n">
-        <v>2072093352</v>
       </c>
       <c r="L120" t="n">
         <v>0.01956155143338956</v>
@@ -16712,10 +16712,10 @@
         <v>0.3638769434336733</v>
       </c>
       <c r="J121" t="n">
+        <v>4360</v>
+      </c>
+      <c r="K121" t="n">
         <v>265045</v>
-      </c>
-      <c r="K121" t="n">
-        <v>1612268735</v>
       </c>
       <c r="L121" t="n">
         <v>0.003638769434336719</v>
@@ -16754,10 +16754,10 @@
         <v>2.439024390243897</v>
       </c>
       <c r="J122" t="n">
+        <v>7126</v>
+      </c>
+      <c r="K122" t="n">
         <v>439862</v>
-      </c>
-      <c r="K122" t="n">
-        <v>2714938229.5</v>
       </c>
       <c r="L122" t="n">
         <v>0.02439024390243905</v>
@@ -16796,10 +16796,10 @@
         <v>-0.4343629343629279</v>
       </c>
       <c r="J123" t="n">
+        <v>4140</v>
+      </c>
+      <c r="K123" t="n">
         <v>257308</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1600391433</v>
       </c>
       <c r="L123" t="n">
         <v>-0.004343629343629307</v>
@@ -16838,10 +16838,10 @@
         <v>-0.01615769914363873</v>
       </c>
       <c r="J124" t="n">
+        <v>3270</v>
+      </c>
+      <c r="K124" t="n">
         <v>202776</v>
-      </c>
-      <c r="K124" t="n">
-        <v>1255234134</v>
       </c>
       <c r="L124" t="n">
         <v>-0.0001615769914363741</v>
@@ -16880,10 +16880,10 @@
         <v>-0.2262443438914036</v>
       </c>
       <c r="J125" t="n">
+        <v>4123</v>
+      </c>
+      <c r="K125" t="n">
         <v>254831</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1569567836.75</v>
       </c>
       <c r="L125" t="n">
         <v>-0.002262443438914019</v>
@@ -16922,10 +16922,10 @@
         <v>-1.328150307742145</v>
       </c>
       <c r="J126" t="n">
+        <v>2974</v>
+      </c>
+      <c r="K126" t="n">
         <v>182306</v>
-      </c>
-      <c r="K126" t="n">
-        <v>1117171168</v>
       </c>
       <c r="L126" t="n">
         <v>-0.01328150307742149</v>
@@ -16964,10 +16964,10 @@
         <v>-0.2462245567957954</v>
       </c>
       <c r="J127" t="n">
+        <v>3263</v>
+      </c>
+      <c r="K127" t="n">
         <v>198530</v>
-      </c>
-      <c r="K127" t="n">
-        <v>1208650640</v>
       </c>
       <c r="L127" t="n">
         <v>-0.002462245567957932</v>
@@ -17006,10 +17006,10 @@
         <v>0.4607536613460491</v>
       </c>
       <c r="J128" t="n">
+        <v>2961</v>
+      </c>
+      <c r="K128" t="n">
         <v>180408</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1100127984</v>
       </c>
       <c r="L128" t="n">
         <v>0.004607536613460583</v>
@@ -17048,10 +17048,10 @@
         <v>0.6060606060606135</v>
       </c>
       <c r="J129" t="n">
+        <v>3777</v>
+      </c>
+      <c r="K129" t="n">
         <v>231176</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1413063300</v>
       </c>
       <c r="L129" t="n">
         <v>0.0060606060606061</v>
@@ -17090,10 +17090,10 @@
         <v>1.367632692933892</v>
       </c>
       <c r="J130" t="n">
+        <v>8160</v>
+      </c>
+      <c r="K130" t="n">
         <v>508618</v>
-      </c>
-      <c r="K130" t="n">
-        <v>3175429328.5</v>
       </c>
       <c r="L130" t="n">
         <v>0.01367632692933896</v>
@@ -17132,10 +17132,10 @@
         <v>0.9958239640218512</v>
       </c>
       <c r="J131" t="n">
+        <v>7897</v>
+      </c>
+      <c r="K131" t="n">
         <v>493593</v>
-      </c>
-      <c r="K131" t="n">
-        <v>3097913066.25</v>
       </c>
       <c r="L131" t="n">
         <v>0.009958239640218469</v>
@@ -17174,10 +17174,10 @@
         <v>0.4770992366412169</v>
       </c>
       <c r="J132" t="n">
+        <v>4582</v>
+      </c>
+      <c r="K132" t="n">
         <v>288960</v>
-      </c>
-      <c r="K132" t="n">
-        <v>1817269440</v>
       </c>
       <c r="L132" t="n">
         <v>0.004770992366412097</v>
@@ -17216,10 +17216,10 @@
         <v>0.03165558721114772</v>
       </c>
       <c r="J133" t="n">
+        <v>3904</v>
+      </c>
+      <c r="K133" t="n">
         <v>247061</v>
-      </c>
-      <c r="K133" t="n">
-        <v>1563957895.25</v>
       </c>
       <c r="L133" t="n">
         <v>0.0003165558721114348</v>
@@ -17258,10 +17258,10 @@
         <v>-0.1898734177215262</v>
       </c>
       <c r="J134" t="n">
+        <v>5004</v>
+      </c>
+      <c r="K134" t="n">
         <v>315629</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1982939192.5</v>
       </c>
       <c r="L134" t="n">
         <v>-0.001898734177215311</v>
@@ -17300,10 +17300,10 @@
         <v>-3.012048192771082</v>
       </c>
       <c r="J135" t="n">
+        <v>4691</v>
+      </c>
+      <c r="K135" t="n">
         <v>290072</v>
-      </c>
-      <c r="K135" t="n">
-        <v>1793515176</v>
       </c>
       <c r="L135" t="n">
         <v>-0.03012048192771077</v>
@@ -17342,10 +17342,10 @@
         <v>-3.644982020268056</v>
       </c>
       <c r="J136" t="n">
+        <v>8720</v>
+      </c>
+      <c r="K136" t="n">
         <v>523785</v>
-      </c>
-      <c r="K136" t="n">
-        <v>3141400537.5</v>
       </c>
       <c r="L136" t="n">
         <v>-0.03644982020268062</v>
@@ -17384,10 +17384,10 @@
         <v>1.950805767599658</v>
       </c>
       <c r="J137" t="n">
+        <v>5542</v>
+      </c>
+      <c r="K137" t="n">
         <v>330418</v>
-      </c>
-      <c r="K137" t="n">
-        <v>1971438997</v>
       </c>
       <c r="L137" t="n">
         <v>0.0195080576759965</v>
@@ -17426,10 +17426,10 @@
         <v>-0.4991680532445995</v>
       </c>
       <c r="J138" t="n">
+        <v>2997</v>
+      </c>
+      <c r="K138" t="n">
         <v>179309</v>
-      </c>
-      <c r="K138" t="n">
-        <v>1074822973.25</v>
       </c>
       <c r="L138" t="n">
         <v>-0.00499168053244603</v>
@@ -17468,10 +17468,10 @@
         <v>1.42140468227425</v>
       </c>
       <c r="J139" t="n">
+        <v>4785</v>
+      </c>
+      <c r="K139" t="n">
         <v>288358</v>
-      </c>
-      <c r="K139" t="n">
-        <v>1740312619.5</v>
       </c>
       <c r="L139" t="n">
         <v>0.01421404682274252</v>
@@ -17510,10 +17510,10 @@
         <v>0.1319043693322313</v>
       </c>
       <c r="J140" t="n">
+        <v>3902</v>
+      </c>
+      <c r="K140" t="n">
         <v>236709</v>
-      </c>
-      <c r="K140" t="n">
-        <v>1436646098.25</v>
       </c>
       <c r="L140" t="n">
         <v>0.001319043693322364</v>
@@ -17552,10 +17552,10 @@
         <v>1.432570393545208</v>
       </c>
       <c r="J141" t="n">
+        <v>5386</v>
+      </c>
+      <c r="K141" t="n">
         <v>329191</v>
-      </c>
-      <c r="K141" t="n">
-        <v>2018352318.75</v>
       </c>
       <c r="L141" t="n">
         <v>0.01432570393545207</v>
@@ -17594,10 +17594,10 @@
         <v>-0.9253246753246758</v>
       </c>
       <c r="J142" t="n">
+        <v>4090</v>
+      </c>
+      <c r="K142" t="n">
         <v>250502</v>
-      </c>
-      <c r="K142" t="n">
-        <v>1535452009</v>
       </c>
       <c r="L142" t="n">
         <v>-0.009253246753246791</v>
@@ -17636,10 +17636,10 @@
         <v>0.278551532033429</v>
       </c>
       <c r="J143" t="n">
+        <v>2539</v>
+      </c>
+      <c r="K143" t="n">
         <v>155182</v>
-      </c>
-      <c r="K143" t="n">
-        <v>948588770.5</v>
       </c>
       <c r="L143" t="n">
         <v>0.00278551532033422</v>
@@ -17678,10 +17678,10 @@
         <v>-0.5555555555555611</v>
       </c>
       <c r="J144" t="n">
+        <v>3514</v>
+      </c>
+      <c r="K144" t="n">
         <v>214308</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1306314414</v>
       </c>
       <c r="L144" t="n">
         <v>-0.005555555555555647</v>
@@ -17720,10 +17720,10 @@
         <v>-0.9037134406835312</v>
       </c>
       <c r="J145" t="n">
+        <v>4717</v>
+      </c>
+      <c r="K145" t="n">
         <v>285752</v>
-      </c>
-      <c r="K145" t="n">
-        <v>1732014310</v>
       </c>
       <c r="L145" t="n">
         <v>-0.00903713440683529</v>
@@ -17762,10 +17762,10 @@
         <v>-0.5471729398109856</v>
       </c>
       <c r="J146" t="n">
+        <v>4215</v>
+      </c>
+      <c r="K146" t="n">
         <v>253305</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1521603135</v>
       </c>
       <c r="L146" t="n">
         <v>-0.005471729398109804</v>
@@ -17804,10 +17804,10 @@
         <v>-1.017005668556185</v>
       </c>
       <c r="J147" t="n">
+        <v>4496</v>
+      </c>
+      <c r="K147" t="n">
         <v>268279</v>
-      </c>
-      <c r="K147" t="n">
-        <v>1601558560.25</v>
       </c>
       <c r="L147" t="n">
         <v>-0.01017005668556181</v>
@@ -17846,10 +17846,10 @@
         <v>5.912076806467922</v>
       </c>
       <c r="J148" t="n">
+        <v>13869</v>
+      </c>
+      <c r="K148" t="n">
         <v>851170</v>
-      </c>
-      <c r="K148" t="n">
-        <v>5230865235</v>
       </c>
       <c r="L148" t="n">
         <v>0.05912076806467925</v>
@@ -17888,10 +17888,10 @@
         <v>-0.03180661577608639</v>
       </c>
       <c r="J149" t="n">
+        <v>7356</v>
+      </c>
+      <c r="K149" t="n">
         <v>463525</v>
-      </c>
-      <c r="K149" t="n">
-        <v>2914413437.5</v>
       </c>
       <c r="L149" t="n">
         <v>-0.0003180661577608657</v>
@@ -17930,10 +17930,10 @@
         <v>1.256761056315621</v>
       </c>
       <c r="J150" t="n">
+        <v>8298</v>
+      </c>
+      <c r="K150" t="n">
         <v>524652</v>
-      </c>
-      <c r="K150" t="n">
-        <v>3329703918</v>
       </c>
       <c r="L150" t="n">
         <v>0.01256761056315625</v>
@@ -17972,10 +17972,10 @@
         <v>-0.3927729772191673</v>
       </c>
       <c r="J151" t="n">
+        <v>6985</v>
+      </c>
+      <c r="K151" t="n">
         <v>447749</v>
-      </c>
-      <c r="K151" t="n">
-        <v>2864250353</v>
       </c>
       <c r="L151" t="n">
         <v>-0.00392772977219169</v>
@@ -18014,10 +18014,10 @@
         <v>0.2839116719242898</v>
       </c>
       <c r="J152" t="n">
+        <v>6716</v>
+      </c>
+      <c r="K152" t="n">
         <v>426358</v>
-      </c>
-      <c r="K152" t="n">
-        <v>2702683362</v>
       </c>
       <c r="L152" t="n">
         <v>0.002839116719242973</v>
@@ -18056,10 +18056,10 @@
         <v>0.1100975149418061</v>
       </c>
       <c r="J153" t="n">
+        <v>6723</v>
+      </c>
+      <c r="K153" t="n">
         <v>428770</v>
-      </c>
-      <c r="K153" t="n">
-        <v>2729764205</v>
       </c>
       <c r="L153" t="n">
         <v>0.001100975149417982</v>
@@ -18098,10 +18098,10 @@
         <v>1.05263157894736</v>
       </c>
       <c r="J154" t="n">
+        <v>11530</v>
+      </c>
+      <c r="K154" t="n">
         <v>740340</v>
-      </c>
-      <c r="K154" t="n">
-        <v>4773342150</v>
       </c>
       <c r="L154" t="n">
         <v>0.01052631578947349</v>
@@ -18140,10 +18140,10 @@
         <v>-1.41480099502487</v>
       </c>
       <c r="J155" t="n">
+        <v>9851</v>
+      </c>
+      <c r="K155" t="n">
         <v>629255</v>
-      </c>
-      <c r="K155" t="n">
-        <v>4029749020</v>
       </c>
       <c r="L155" t="n">
         <v>-0.01414800995024867</v>
@@ -18182,10 +18182,10 @@
         <v>-0.6938968616937357</v>
       </c>
       <c r="J156" t="n">
+        <v>7425</v>
+      </c>
+      <c r="K156" t="n">
         <v>467612</v>
-      </c>
-      <c r="K156" t="n">
-        <v>2946890824</v>
       </c>
       <c r="L156" t="n">
         <v>-0.006938968616937324</v>
@@ -18224,10 +18224,10 @@
         <v>-1.953311100524054</v>
       </c>
       <c r="J157" t="n">
+        <v>8388</v>
+      </c>
+      <c r="K157" t="n">
         <v>523786</v>
-      </c>
-      <c r="K157" t="n">
-        <v>3269341265.5</v>
       </c>
       <c r="L157" t="n">
         <v>-0.01953311100524058</v>
@@ -18266,10 +18266,10 @@
         <v>-1.328150307742145</v>
       </c>
       <c r="J158" t="n">
+        <v>7736</v>
+      </c>
+      <c r="K158" t="n">
         <v>473891</v>
-      </c>
-      <c r="K158" t="n">
-        <v>2904477939</v>
       </c>
       <c r="L158" t="n">
         <v>-0.01328150307742149</v>
@@ -18308,10 +18308,10 @@
         <v>-1.017728168089305</v>
       </c>
       <c r="J159" t="n">
+        <v>7057</v>
+      </c>
+      <c r="K159" t="n">
         <v>427755</v>
-      </c>
-      <c r="K159" t="n">
-        <v>2597328360</v>
       </c>
       <c r="L159" t="n">
         <v>-0.01017728168089305</v>
@@ -18350,10 +18350,10 @@
         <v>-0.663349917081258</v>
       </c>
       <c r="J160" t="n">
+        <v>9085</v>
+      </c>
+      <c r="K160" t="n">
         <v>546035</v>
-      </c>
-      <c r="K160" t="n">
-        <v>3283717981.25</v>
       </c>
       <c r="L160" t="n">
         <v>-0.006633499170812573</v>
@@ -18392,10 +18392,10 @@
         <v>-1.101836393989978</v>
       </c>
       <c r="J161" t="n">
+        <v>8996</v>
+      </c>
+      <c r="K161" t="n">
         <v>537068</v>
-      </c>
-      <c r="K161" t="n">
-        <v>3204416222</v>
       </c>
       <c r="L161" t="n">
         <v>-0.01101836393989974</v>
@@ -18434,10 +18434,10 @@
         <v>-0.7596218771100656</v>
       </c>
       <c r="J162" t="n">
+        <v>13659</v>
+      </c>
+      <c r="K162" t="n">
         <v>808043</v>
-      </c>
-      <c r="K162" t="n">
-        <v>4786644721.25</v>
       </c>
       <c r="L162" t="n">
         <v>-0.007596218771100616</v>
@@ -18476,10 +18476,10 @@
         <v>-1.411804728695353</v>
       </c>
       <c r="J163" t="n">
+        <v>12460</v>
+      </c>
+      <c r="K163" t="n">
         <v>727329</v>
-      </c>
-      <c r="K163" t="n">
-        <v>4246874031</v>
       </c>
       <c r="L163" t="n">
         <v>-0.01411804728695354</v>
@@ -18518,10 +18518,10 @@
         <v>-1.656314699792962</v>
       </c>
       <c r="J164" t="n">
+        <v>11064</v>
+      </c>
+      <c r="K164" t="n">
         <v>637255</v>
-      </c>
-      <c r="K164" t="n">
-        <v>3670907427.5</v>
       </c>
       <c r="L164" t="n">
         <v>-0.0165631469979296</v>
@@ -18560,10 +18560,10 @@
         <v>-1.14035087719298</v>
       </c>
       <c r="J165" t="n">
+        <v>15472</v>
+      </c>
+      <c r="K165" t="n">
         <v>878750</v>
-      </c>
-      <c r="K165" t="n">
-        <v>4993277187.5</v>
       </c>
       <c r="L165" t="n">
         <v>-0.01140350877192975</v>
@@ -18602,10 +18602,10 @@
         <v>2.768411712511083</v>
       </c>
       <c r="J166" t="n">
+        <v>19951</v>
+      </c>
+      <c r="K166" t="n">
         <v>1137825</v>
-      </c>
-      <c r="K166" t="n">
-        <v>6488731518.75</v>
       </c>
       <c r="L166" t="n">
         <v>0.02768411712511076</v>
@@ -18644,10 +18644,10 @@
         <v>0.08634087376964991</v>
       </c>
       <c r="J167" t="n">
+        <v>14721</v>
+      </c>
+      <c r="K167" t="n">
         <v>852045</v>
-      </c>
-      <c r="K167" t="n">
-        <v>4961245023.75</v>
       </c>
       <c r="L167" t="n">
         <v>0.0008634087376964139</v>
@@ -18686,10 +18686,10 @@
         <v>-2.881297446514841</v>
       </c>
       <c r="J168" t="n">
+        <v>10708</v>
+      </c>
+      <c r="K168" t="n">
         <v>609580</v>
-      </c>
-      <c r="K168" t="n">
-        <v>3475977555</v>
       </c>
       <c r="L168" t="n">
         <v>-0.02881297446514841</v>
@@ -18728,10 +18728,10 @@
         <v>1.740984189021148</v>
       </c>
       <c r="J169" t="n">
+        <v>8746</v>
+      </c>
+      <c r="K169" t="n">
         <v>498835</v>
-      </c>
-      <c r="K169" t="n">
-        <v>2841613577.5</v>
       </c>
       <c r="L169" t="n">
         <v>0.01740984189021155</v>
@@ -18770,10 +18770,10 @@
         <v>0.2269949362667984</v>
       </c>
       <c r="J170" t="n">
+        <v>8546</v>
+      </c>
+      <c r="K170" t="n">
         <v>489243</v>
-      </c>
-      <c r="K170" t="n">
-        <v>2789052032.25</v>
       </c>
       <c r="L170" t="n">
         <v>0.002269949362667889</v>
@@ -18812,10 +18812,10 @@
         <v>0.975609756097565</v>
       </c>
       <c r="J171" t="n">
+        <v>8984</v>
+      </c>
+      <c r="K171" t="n">
         <v>517746</v>
-      </c>
-      <c r="K171" t="n">
-        <v>2985193999.5</v>
       </c>
       <c r="L171" t="n">
         <v>0.009756097560975618</v>
@@ -18854,10 +18854,10 @@
         <v>-1.466528640441686</v>
       </c>
       <c r="J172" t="n">
+        <v>6296</v>
+      </c>
+      <c r="K172" t="n">
         <v>360904</v>
-      </c>
-      <c r="K172" t="n">
-        <v>2071949864</v>
       </c>
       <c r="L172" t="n">
         <v>-0.01466528640441689</v>
@@ -18896,10 +18896,10 @@
         <v>0.2451409560497296</v>
       </c>
       <c r="J173" t="n">
+        <v>6378</v>
+      </c>
+      <c r="K173" t="n">
         <v>366117</v>
-      </c>
-      <c r="K173" t="n">
-        <v>2098674173.25</v>
       </c>
       <c r="L173" t="n">
         <v>0.002451409560497275</v>
@@ -18938,10 +18938,10 @@
         <v>1.659388646288214</v>
       </c>
       <c r="J174" t="n">
+        <v>11240</v>
+      </c>
+      <c r="K174" t="n">
         <v>648861</v>
-      </c>
-      <c r="K174" t="n">
-        <v>3749605503.75</v>
       </c>
       <c r="L174" t="n">
         <v>0.01659388646288207</v>
@@ -18980,10 +18980,10 @@
         <v>0.8591065292096219</v>
       </c>
       <c r="J175" t="n">
+        <v>9815</v>
+      </c>
+      <c r="K175" t="n">
         <v>573680</v>
-      </c>
-      <c r="K175" t="n">
-        <v>3367501600</v>
       </c>
       <c r="L175" t="n">
         <v>0.008591065292096189</v>
@@ -19022,10 +19022,10 @@
         <v>-0.2725724020442993</v>
       </c>
       <c r="J176" t="n">
+        <v>5964</v>
+      </c>
+      <c r="K176" t="n">
         <v>348690</v>
-      </c>
-      <c r="K176" t="n">
-        <v>2044456642.5</v>
       </c>
       <c r="L176" t="n">
         <v>-0.002725724020443021</v>
@@ -19064,10 +19064,10 @@
         <v>-0.8711991800478271</v>
       </c>
       <c r="J177" t="n">
+        <v>5894</v>
+      </c>
+      <c r="K177" t="n">
         <v>343568</v>
-      </c>
-      <c r="K177" t="n">
-        <v>2004461604</v>
       </c>
       <c r="L177" t="n">
         <v>-0.008711991800478325</v>
@@ -19106,10 +19106,10 @@
         <v>-0.3791142512493518</v>
       </c>
       <c r="J178" t="n">
+        <v>5849</v>
+      </c>
+      <c r="K178" t="n">
         <v>338981</v>
-      </c>
-      <c r="K178" t="n">
-        <v>1963716933</v>
       </c>
       <c r="L178" t="n">
         <v>-0.003791142512493573</v>
@@ -19148,10 +19148,10 @@
         <v>-0.2594706798131909</v>
       </c>
       <c r="J179" t="n">
+        <v>7304</v>
+      </c>
+      <c r="K179" t="n">
         <v>421579</v>
-      </c>
-      <c r="K179" t="n">
-        <v>2432721619.5</v>
       </c>
       <c r="L179" t="n">
         <v>-0.002594706798131896</v>
@@ -19190,10 +19190,10 @@
         <v>-1.9771071800208</v>
       </c>
       <c r="J180" t="n">
+        <v>8916</v>
+      </c>
+      <c r="K180" t="n">
         <v>508987</v>
-      </c>
-      <c r="K180" t="n">
-        <v>2907333744</v>
       </c>
       <c r="L180" t="n">
         <v>-0.01977107180020798</v>
@@ -19232,10 +19232,10 @@
         <v>-0.2830856334041112</v>
       </c>
       <c r="J181" t="n">
+        <v>6449</v>
+      </c>
+      <c r="K181" t="n">
         <v>363641</v>
-      </c>
-      <c r="K181" t="n">
-        <v>2054117098.75</v>
       </c>
       <c r="L181" t="n">
         <v>-0.002830856334041121</v>
@@ -19274,10 +19274,10 @@
         <v>-3.584102200141938</v>
       </c>
       <c r="J182" t="n">
+        <v>13526</v>
+      </c>
+      <c r="K182" t="n">
         <v>742062</v>
-      </c>
-      <c r="K182" t="n">
-        <v>4073920380</v>
       </c>
       <c r="L182" t="n">
         <v>-0.03584102200141936</v>
@@ -19316,10 +19316,10 @@
         <v>-1.711446448288566</v>
       </c>
       <c r="J183" t="n">
+        <v>11146</v>
+      </c>
+      <c r="K183" t="n">
         <v>601399</v>
-      </c>
-      <c r="K183" t="n">
-        <v>3251914742.75</v>
       </c>
       <c r="L183" t="n">
         <v>-0.01711446448288567</v>
@@ -19358,10 +19358,10 @@
         <v>-1.179554390563557</v>
       </c>
       <c r="J184" t="n">
+        <v>8913</v>
+      </c>
+      <c r="K184" t="n">
         <v>471518</v>
-      </c>
-      <c r="K184" t="n">
-        <v>2498691761.5</v>
       </c>
       <c r="L184" t="n">
         <v>-0.01179554390563553</v>
@@ -19400,10 +19400,10 @@
         <v>1.40204622963244</v>
       </c>
       <c r="J185" t="n">
+        <v>9086</v>
+      </c>
+      <c r="K185" t="n">
         <v>484860</v>
-      </c>
-      <c r="K185" t="n">
-        <v>2597273805</v>
       </c>
       <c r="L185" t="n">
         <v>0.01402046229632448</v>
@@ -19442,10 +19442,10 @@
         <v>3.437967115097153</v>
       </c>
       <c r="J186" t="n">
+        <v>11569</v>
+      </c>
+      <c r="K186" t="n">
         <v>629119</v>
-      </c>
-      <c r="K186" t="n">
-        <v>3419733604.25</v>
       </c>
       <c r="L186" t="n">
         <v>0.03437967115097162</v>
@@ -19484,10 +19484,10 @@
         <v>-1.119942196531787</v>
       </c>
       <c r="J187" t="n">
+        <v>7798</v>
+      </c>
+      <c r="K187" t="n">
         <v>426233</v>
-      </c>
-      <c r="K187" t="n">
-        <v>2324568223.75</v>
       </c>
       <c r="L187" t="n">
         <v>-0.01119942196531787</v>
@@ -19526,10 +19526,10 @@
         <v>2.941176470588234</v>
       </c>
       <c r="J188" t="n">
+        <v>8499</v>
+      </c>
+      <c r="K188" t="n">
         <v>473605</v>
-      </c>
-      <c r="K188" t="n">
-        <v>2641531887.5</v>
       </c>
       <c r="L188" t="n">
         <v>0.02941176470588225</v>
@@ -19568,10 +19568,10 @@
         <v>-1.277728482697425</v>
       </c>
       <c r="J189" t="n">
+        <v>5743</v>
+      </c>
+      <c r="K189" t="n">
         <v>321259</v>
-      </c>
-      <c r="K189" t="n">
-        <v>1796078754.25</v>
       </c>
       <c r="L189" t="n">
         <v>-0.01277728482697427</v>
@@ -19610,10 +19610,10 @@
         <v>-0.9527233507100505</v>
       </c>
       <c r="J190" t="n">
+        <v>4818</v>
+      </c>
+      <c r="K190" t="n">
         <v>266691</v>
-      </c>
-      <c r="K190" t="n">
-        <v>1477268121.75</v>
       </c>
       <c r="L190" t="n">
         <v>-0.009527233507100497</v>
@@ -19652,10 +19652,10 @@
         <v>-0.3448275862069053</v>
       </c>
       <c r="J191" t="n">
+        <v>4439</v>
+      </c>
+      <c r="K191" t="n">
         <v>244164</v>
-      </c>
-      <c r="K191" t="n">
-        <v>1344061779</v>
       </c>
       <c r="L191" t="n">
         <v>-0.003448275862069083</v>
@@ -19694,10 +19694,10 @@
         <v>0.8741577126206592</v>
       </c>
       <c r="J192" t="n">
+        <v>5575</v>
+      </c>
+      <c r="K192" t="n">
         <v>307751</v>
-      </c>
-      <c r="K192" t="n">
-        <v>1697015951.75</v>
       </c>
       <c r="L192" t="n">
         <v>0.00874157712620649</v>
@@ -19736,10 +19736,10 @@
         <v>1.281819823072758</v>
       </c>
       <c r="J193" t="n">
+        <v>9035</v>
+      </c>
+      <c r="K193" t="n">
         <v>504111</v>
-      </c>
-      <c r="K193" t="n">
-        <v>2823147627.75</v>
       </c>
       <c r="L193" t="n">
         <v>0.01281819823072761</v>
@@ -19778,10 +19778,10 @@
         <v>1.033868092691619</v>
       </c>
       <c r="J194" t="n">
+        <v>6986</v>
+      </c>
+      <c r="K194" t="n">
         <v>393793</v>
-      </c>
-      <c r="K194" t="n">
-        <v>2219417348</v>
       </c>
       <c r="L194" t="n">
         <v>0.01033868092691614</v>
@@ -19820,10 +19820,10 @@
         <v>-1.51729004940014</v>
       </c>
       <c r="J195" t="n">
+        <v>6148</v>
+      </c>
+      <c r="K195" t="n">
         <v>343647</v>
-      </c>
-      <c r="K195" t="n">
-        <v>1927258287.75</v>
       </c>
       <c r="L195" t="n">
         <v>-0.01517290049400144</v>
@@ -19862,10 +19862,10 @@
         <v>-1.576495879613047</v>
       </c>
       <c r="J196" t="n">
+        <v>6263</v>
+      </c>
+      <c r="K196" t="n">
         <v>347395</v>
-      </c>
-      <c r="K196" t="n">
-        <v>1930995107.5</v>
       </c>
       <c r="L196" t="n">
         <v>-0.01576495879613049</v>
@@ -19904,10 +19904,10 @@
         <v>-4.295595194757917</v>
       </c>
       <c r="J197" t="n">
+        <v>9154</v>
+      </c>
+      <c r="K197" t="n">
         <v>487702</v>
-      </c>
-      <c r="K197" t="n">
-        <v>2596037746</v>
       </c>
       <c r="L197" t="n">
         <v>-0.04295595194757917</v>
@@ -19946,10 +19946,10 @@
         <v>1.635602890833015</v>
       </c>
       <c r="J198" t="n">
+        <v>6541</v>
+      </c>
+      <c r="K198" t="n">
         <v>348355</v>
-      </c>
-      <c r="K198" t="n">
-        <v>1852029357.5</v>
       </c>
       <c r="L198" t="n">
         <v>0.01635602890833021</v>
@@ -19988,10 +19988,10 @@
         <v>0.860778443113774</v>
       </c>
       <c r="J199" t="n">
+        <v>7642</v>
+      </c>
+      <c r="K199" t="n">
         <v>411526</v>
-      </c>
-      <c r="K199" t="n">
-        <v>2222240400</v>
       </c>
       <c r="L199" t="n">
         <v>0.008607784431137633</v>
@@ -20030,10 +20030,10 @@
         <v>-4.582560296846009</v>
       </c>
       <c r="J200" t="n">
+        <v>12428</v>
+      </c>
+      <c r="K200" t="n">
         <v>649417</v>
-      </c>
-      <c r="K200" t="n">
-        <v>3405380393.75</v>
       </c>
       <c r="L200" t="n">
         <v>-0.04582560296846006</v>
@@ -20072,10 +20072,10 @@
         <v>6.902586039276681</v>
       </c>
       <c r="J201" t="n">
+        <v>18688</v>
+      </c>
+      <c r="K201" t="n">
         <v>991196</v>
-      </c>
-      <c r="K201" t="n">
-        <v>5260029373</v>
       </c>
       <c r="L201" t="n">
         <v>0.0690258603927667</v>
@@ -20114,10 +20114,10 @@
         <v>1.054929065114597</v>
       </c>
       <c r="J202" t="n">
+        <v>12667</v>
+      </c>
+      <c r="K202" t="n">
         <v>697271</v>
-      </c>
-      <c r="K202" t="n">
-        <v>3841963210</v>
       </c>
       <c r="L202" t="n">
         <v>0.01054929065114596</v>
@@ -20156,10 +20156,10 @@
         <v>-0.9719222462203008</v>
       </c>
       <c r="J203" t="n">
+        <v>12521</v>
+      </c>
+      <c r="K203" t="n">
         <v>692924</v>
-      </c>
-      <c r="K203" t="n">
-        <v>3860626066</v>
       </c>
       <c r="L203" t="n">
         <v>-0.009719222462203025</v>
@@ -20198,10 +20198,10 @@
         <v>4.561977462740818</v>
       </c>
       <c r="J204" t="n">
+        <v>17740</v>
+      </c>
+      <c r="K204" t="n">
         <v>1005517</v>
-      </c>
-      <c r="K204" t="n">
-        <v>5689717944.5</v>
       </c>
       <c r="L204" t="n">
         <v>0.04561977462740807</v>
@@ -20240,10 +20240,10 @@
         <v>-0.6257604727968007</v>
       </c>
       <c r="J205" t="n">
+        <v>13341</v>
+      </c>
+      <c r="K205" t="n">
         <v>765170</v>
-      </c>
-      <c r="K205" t="n">
-        <v>4393414847.5</v>
       </c>
       <c r="L205" t="n">
         <v>-0.006257604727967991</v>
@@ -20282,10 +20282,10 @@
         <v>-1.731677453209729</v>
       </c>
       <c r="J206" t="n">
+        <v>8054</v>
+      </c>
+      <c r="K206" t="n">
         <v>454916</v>
-      </c>
-      <c r="K206" t="n">
-        <v>2566294885</v>
       </c>
       <c r="L206" t="n">
         <v>-0.01731677453209723</v>
@@ -20324,10 +20324,10 @@
         <v>-0.4627981488074012</v>
       </c>
       <c r="J207" t="n">
+        <v>7154</v>
+      </c>
+      <c r="K207" t="n">
         <v>401467</v>
-      </c>
-      <c r="K207" t="n">
-        <v>2245003464</v>
       </c>
       <c r="L207" t="n">
         <v>-0.004627981488073973</v>
@@ -20366,10 +20366,10 @@
         <v>2.378397711015733</v>
       </c>
       <c r="J208" t="n">
+        <v>12879</v>
+      </c>
+      <c r="K208" t="n">
         <v>734463</v>
-      </c>
-      <c r="K208" t="n">
-        <v>4171933455.75</v>
       </c>
       <c r="L208" t="n">
         <v>0.02378397711015734</v>
@@ -20408,10 +20408,10 @@
         <v>-0.8558951965065537</v>
       </c>
       <c r="J209" t="n">
+        <v>8473</v>
+      </c>
+      <c r="K209" t="n">
         <v>480755</v>
-      </c>
-      <c r="K209" t="n">
-        <v>2737418970</v>
       </c>
       <c r="L209" t="n">
         <v>-0.008558951965065509</v>
@@ -20450,10 +20450,10 @@
         <v>0.1761804087385508</v>
       </c>
       <c r="J210" t="n">
+        <v>10298</v>
+      </c>
+      <c r="K210" t="n">
         <v>587795</v>
-      </c>
-      <c r="K210" t="n">
-        <v>3360717912.5</v>
       </c>
       <c r="L210" t="n">
         <v>0.001761804087385466</v>
@@ -20492,10 +20492,10 @@
         <v>-3.271192402391839</v>
       </c>
       <c r="J211" t="n">
+        <v>14292</v>
+      </c>
+      <c r="K211" t="n">
         <v>796044</v>
-      </c>
-      <c r="K211" t="n">
-        <v>4430979915</v>
       </c>
       <c r="L211" t="n">
         <v>-0.03271192402391843</v>
@@ -20534,10 +20534,10 @@
         <v>1.781818181818176</v>
       </c>
       <c r="J212" t="n">
+        <v>10338</v>
+      </c>
+      <c r="K212" t="n">
         <v>574457</v>
-      </c>
-      <c r="K212" t="n">
-        <v>3185938522</v>
       </c>
       <c r="L212" t="n">
         <v>0.01781818181818173</v>
@@ -20576,10 +20576,10 @@
         <v>2.768846016434449</v>
       </c>
       <c r="J213" t="n">
+        <v>17862</v>
+      </c>
+      <c r="K213" t="n">
         <v>1029480</v>
-      </c>
-      <c r="K213" t="n">
-        <v>5928775320</v>
       </c>
       <c r="L213" t="n">
         <v>0.02768846016434456</v>
@@ -20618,10 +20618,10 @@
         <v>-0.4519381192421311</v>
       </c>
       <c r="J214" t="n">
+        <v>10026</v>
+      </c>
+      <c r="K214" t="n">
         <v>576718</v>
-      </c>
-      <c r="K214" t="n">
-        <v>3311370576.5</v>
       </c>
       <c r="L214" t="n">
         <v>-0.004519381192421346</v>
@@ -20660,10 +20660,10 @@
         <v>-1.990570979570456</v>
       </c>
       <c r="J215" t="n">
+        <v>11182</v>
+      </c>
+      <c r="K215" t="n">
         <v>632524</v>
-      </c>
-      <c r="K215" t="n">
-        <v>3572811814</v>
       </c>
       <c r="L215" t="n">
         <v>-0.01990570979570461</v>
@@ -20702,10 +20702,10 @@
         <v>0.01781578478531625</v>
       </c>
       <c r="J216" t="n">
+        <v>7714</v>
+      </c>
+      <c r="K216" t="n">
         <v>433049</v>
-      </c>
-      <c r="K216" t="n">
-        <v>2429188365.5</v>
       </c>
       <c r="L216" t="n">
         <v>0.0001781578478532442</v>
@@ -20744,10 +20744,10 @@
         <v>-1.050944068400434</v>
       </c>
       <c r="J217" t="n">
+        <v>7748</v>
+      </c>
+      <c r="K217" t="n">
         <v>432751</v>
-      </c>
-      <c r="K217" t="n">
-        <v>2419186277.75</v>
       </c>
       <c r="L217" t="n">
         <v>-0.01050944068400439</v>
@@ -20786,10 +20786,10 @@
         <v>-0.5580558055805495</v>
       </c>
       <c r="J218" t="n">
+        <v>9464</v>
+      </c>
+      <c r="K218" t="n">
         <v>523563</v>
-      </c>
-      <c r="K218" t="n">
-        <v>2894256264</v>
       </c>
       <c r="L218" t="n">
         <v>-0.005580558055805485</v>
@@ -20828,10 +20828,10 @@
         <v>1.737871107892833</v>
       </c>
       <c r="J219" t="n">
+        <v>17209</v>
+      </c>
+      <c r="K219" t="n">
         <v>963938</v>
-      </c>
-      <c r="K219" t="n">
-        <v>5437092289</v>
       </c>
       <c r="L219" t="n">
         <v>0.0173787110789283</v>
@@ -20870,10 +20870,10 @@
         <v>-0.6227758007117463</v>
       </c>
       <c r="J220" t="n">
+        <v>9947</v>
+      </c>
+      <c r="K220" t="n">
         <v>557798</v>
-      </c>
-      <c r="K220" t="n">
-        <v>3121158709</v>
       </c>
       <c r="L220" t="n">
         <v>-0.006227758007117501</v>
@@ -20912,10 +20912,10 @@
         <v>-1.199641897940916</v>
       </c>
       <c r="J221" t="n">
+        <v>8205</v>
+      </c>
+      <c r="K221" t="n">
         <v>455530</v>
-      </c>
-      <c r="K221" t="n">
-        <v>2527166557.5</v>
       </c>
       <c r="L221" t="n">
         <v>-0.01199641897940917</v>
@@ -20954,10 +20954,10 @@
         <v>-0.9786154403769466</v>
       </c>
       <c r="J222" t="n">
+        <v>16447</v>
+      </c>
+      <c r="K222" t="n">
         <v>903120</v>
-      </c>
-      <c r="K222" t="n">
-        <v>5002607460</v>
       </c>
       <c r="L222" t="n">
         <v>-0.009786154403769509</v>
@@ -20996,10 +20996,10 @@
         <v>0.2745241581259125</v>
       </c>
       <c r="J223" t="n">
+        <v>10812</v>
+      </c>
+      <c r="K223" t="n">
         <v>591509</v>
-      </c>
-      <c r="K223" t="n">
-        <v>3228160367.5</v>
       </c>
       <c r="L223" t="n">
         <v>0.002745241581259217</v>
@@ -21038,10 +21038,10 @@
         <v>-2.025917138163898</v>
       </c>
       <c r="J224" t="n">
+        <v>13131</v>
+      </c>
+      <c r="K224" t="n">
         <v>712485</v>
-      </c>
-      <c r="K224" t="n">
-        <v>3864696761.25</v>
       </c>
       <c r="L224" t="n">
         <v>-0.02025917138163902</v>
@@ -21080,10 +21080,10 @@
         <v>-0.4657228017883756</v>
       </c>
       <c r="J225" t="n">
+        <v>12420</v>
+      </c>
+      <c r="K225" t="n">
         <v>665748</v>
-      </c>
-      <c r="K225" t="n">
-        <v>3567077784</v>
       </c>
       <c r="L225" t="n">
         <v>-0.004657228017883708</v>
@@ -21122,10 +21122,10 @@
         <v>0.09358038555118316</v>
       </c>
       <c r="J226" t="n">
+        <v>11636</v>
+      </c>
+      <c r="K226" t="n">
         <v>623452</v>
-      </c>
-      <c r="K226" t="n">
-        <v>3344664117</v>
       </c>
       <c r="L226" t="n">
         <v>0.0009358038555118409</v>
@@ -21164,10 +21164,10 @@
         <v>-1.645474943904255</v>
       </c>
       <c r="J227" t="n">
+        <v>15100</v>
+      </c>
+      <c r="K227" t="n">
         <v>802415</v>
-      </c>
-      <c r="K227" t="n">
-        <v>4262428480</v>
       </c>
       <c r="L227" t="n">
         <v>-0.01645474943904257</v>
@@ -21206,10 +21206,10 @@
         <v>1.368821292775663</v>
       </c>
       <c r="J228" t="n">
+        <v>19318</v>
+      </c>
+      <c r="K228" t="n">
         <v>1023063</v>
-      </c>
-      <c r="K228" t="n">
-        <v>5407655252.25</v>
       </c>
       <c r="L228" t="n">
         <v>0.01368821292775668</v>
@@ -21248,10 +21248,10 @@
         <v>4.857464366091516</v>
       </c>
       <c r="J229" t="n">
+        <v>45137</v>
+      </c>
+      <c r="K229" t="n">
         <v>2465400</v>
-      </c>
-      <c r="K229" t="n">
-        <v>13588052100</v>
       </c>
       <c r="L229" t="n">
         <v>0.04857464366091513</v>
@@ -21290,10 +21290,10 @@
         <v>-0.4471472008585227</v>
       </c>
       <c r="J230" t="n">
+        <v>23802</v>
+      </c>
+      <c r="K230" t="n">
         <v>1327791</v>
-      </c>
-      <c r="K230" t="n">
-        <v>7438617129.75</v>
       </c>
       <c r="L230" t="n">
         <v>-0.00447147200858522</v>
@@ -21332,10 +21332,10 @@
         <v>-2.766798418972331</v>
       </c>
       <c r="J231" t="n">
+        <v>16719</v>
+      </c>
+      <c r="K231" t="n">
         <v>917227</v>
-      </c>
-      <c r="K231" t="n">
-        <v>5052544929.5</v>
       </c>
       <c r="L231" t="n">
         <v>-0.02766798418972327</v>
@@ -21374,10 +21374,10 @@
         <v>-0.6097560975609725</v>
       </c>
       <c r="J232" t="n">
+        <v>14228</v>
+      </c>
+      <c r="K232" t="n">
         <v>765989</v>
-      </c>
-      <c r="K232" t="n">
-        <v>4149362413</v>
       </c>
       <c r="L232" t="n">
         <v>-0.006097560975609762</v>
@@ -21416,10 +21416,10 @@
         <v>-2.900167317345236</v>
       </c>
       <c r="J233" t="n">
+        <v>14868</v>
+      </c>
+      <c r="K233" t="n">
         <v>786609</v>
-      </c>
-      <c r="K233" t="n">
-        <v>4157228565</v>
       </c>
       <c r="L233" t="n">
         <v>-0.02900167317345237</v>
@@ -21458,10 +21458,10 @@
         <v>-1.608271108558293</v>
       </c>
       <c r="J234" t="n">
+        <v>13510</v>
+      </c>
+      <c r="K234" t="n">
         <v>699095</v>
-      </c>
-      <c r="K234" t="n">
-        <v>3623584158.75</v>
       </c>
       <c r="L234" t="n">
         <v>-0.0160827110855829</v>
@@ -21500,10 +21500,10 @@
         <v>-1.245378478303173</v>
       </c>
       <c r="J235" t="n">
+        <v>16207</v>
+      </c>
+      <c r="K235" t="n">
         <v>827046</v>
-      </c>
-      <c r="K235" t="n">
-        <v>4217934600</v>
       </c>
       <c r="L235" t="n">
         <v>-0.01245378478303172</v>
@@ -21542,10 +21542,10 @@
         <v>0.9852216748768473</v>
       </c>
       <c r="J236" t="n">
+        <v>19475</v>
+      </c>
+      <c r="K236" t="n">
         <v>994025</v>
-      </c>
-      <c r="K236" t="n">
-        <v>5103075843.75</v>
       </c>
       <c r="L236" t="n">
         <v>0.009852216748768461</v>
@@ -21584,10 +21584,10 @@
         <v>-1.912195121951214</v>
       </c>
       <c r="J237" t="n">
+        <v>13336</v>
+      </c>
+      <c r="K237" t="n">
         <v>677620</v>
-      </c>
-      <c r="K237" t="n">
-        <v>3442309600</v>
       </c>
       <c r="L237" t="n">
         <v>-0.0191219512195121</v>
@@ -21626,10 +21626,10 @@
         <v>-2.068828327034029</v>
       </c>
       <c r="J238" t="n">
+        <v>16930</v>
+      </c>
+      <c r="K238" t="n">
         <v>838355</v>
-      </c>
-      <c r="K238" t="n">
-        <v>4143150410</v>
       </c>
       <c r="L238" t="n">
         <v>-0.02068828327034034</v>
@@ -21668,10 +21668,10 @@
         <v>-0.4671947999187424</v>
       </c>
       <c r="J239" t="n">
+        <v>14584</v>
+      </c>
+      <c r="K239" t="n">
         <v>713746</v>
-      </c>
-      <c r="K239" t="n">
-        <v>3505385042.5</v>
       </c>
       <c r="L239" t="n">
         <v>-0.004671947999187465</v>
@@ -21710,10 +21710,10 @@
         <v>2.795918367346934</v>
       </c>
       <c r="J240" t="n">
+        <v>19368</v>
+      </c>
+      <c r="K240" t="n">
         <v>961153</v>
-      </c>
-      <c r="K240" t="n">
-        <v>4781736175</v>
       </c>
       <c r="L240" t="n">
         <v>0.02795918367346939</v>
@@ -21752,10 +21752,10 @@
         <v>-4.705181655747464</v>
       </c>
       <c r="J241" t="n">
+        <v>19961</v>
+      </c>
+      <c r="K241" t="n">
         <v>978697</v>
-      </c>
-      <c r="K241" t="n">
-        <v>4807604338.25</v>
       </c>
       <c r="L241" t="n">
         <v>-0.04705181655747459</v>
@@ -21794,10 +21794,10 @@
         <v>4.562499999999995</v>
       </c>
       <c r="J242" t="n">
+        <v>26482</v>
+      </c>
+      <c r="K242" t="n">
         <v>1300405</v>
-      </c>
-      <c r="K242" t="n">
-        <v>6383363043.75</v>
       </c>
       <c r="L242" t="n">
         <v>0.04562500000000003</v>
@@ -21836,10 +21836,10 @@
         <v>-2.032277346084869</v>
       </c>
       <c r="J243" t="n">
+        <v>19030</v>
+      </c>
+      <c r="K243" t="n">
         <v>946653</v>
-      </c>
-      <c r="K243" t="n">
-        <v>4725928439.25</v>
       </c>
       <c r="L243" t="n">
         <v>-0.02032277346084865</v>
@@ -21878,10 +21878,10 @@
         <v>-1.565995525727076</v>
       </c>
       <c r="J244" t="n">
+        <v>12579</v>
+      </c>
+      <c r="K244" t="n">
         <v>611443</v>
-      </c>
-      <c r="K244" t="n">
-        <v>2968861486.5</v>
       </c>
       <c r="L244" t="n">
         <v>-0.01565995525727071</v>
@@ -21920,10 +21920,10 @@
         <v>-2.479338842975198</v>
       </c>
       <c r="J245" t="n">
+        <v>17112</v>
+      </c>
+      <c r="K245" t="n">
         <v>815364</v>
-      </c>
-      <c r="K245" t="n">
-        <v>3886840188</v>
       </c>
       <c r="L245" t="n">
         <v>-0.02479338842975198</v>
@@ -21962,10 +21962,10 @@
         <v>-1.207627118644068</v>
       </c>
       <c r="J246" t="n">
+        <v>13655</v>
+      </c>
+      <c r="K246" t="n">
         <v>639249</v>
-      </c>
-      <c r="K246" t="n">
-        <v>3004789924.5</v>
       </c>
       <c r="L246" t="n">
         <v>-0.01207627118644072</v>
@@ -22004,10 +22004,10 @@
         <v>0.9650439631138661</v>
       </c>
       <c r="J247" t="n">
+        <v>19676</v>
+      </c>
+      <c r="K247" t="n">
         <v>930264</v>
-      </c>
-      <c r="K247" t="n">
-        <v>4425265848</v>
       </c>
       <c r="L247" t="n">
         <v>0.009650439631138763</v>
@@ -22046,10 +22046,10 @@
         <v>-2.4214103653356</v>
       </c>
       <c r="J248" t="n">
+        <v>14787</v>
+      </c>
+      <c r="K248" t="n">
         <v>684211</v>
-      </c>
-      <c r="K248" t="n">
-        <v>3178331147.75</v>
       </c>
       <c r="L248" t="n">
         <v>-0.02421410365335597</v>
@@ -22088,10 +22088,10 @@
         <v>0.9577710056595665</v>
       </c>
       <c r="J249" t="n">
+        <v>13401</v>
+      </c>
+      <c r="K249" t="n">
         <v>621286</v>
-      </c>
-      <c r="K249" t="n">
-        <v>2866924247</v>
       </c>
       <c r="L249" t="n">
         <v>0.00957771005659569</v>
@@ -22130,10 +22130,10 @@
         <v>1.358344113842163</v>
       </c>
       <c r="J250" t="n">
+        <v>13351</v>
+      </c>
+      <c r="K250" t="n">
         <v>621576</v>
-      </c>
-      <c r="K250" t="n">
-        <v>2896544160</v>
       </c>
       <c r="L250" t="n">
         <v>0.01358344113842169</v>
@@ -22172,10 +22172,10 @@
         <v>-0.06381620931716898</v>
       </c>
       <c r="J251" t="n">
+        <v>10106</v>
+      </c>
+      <c r="K251" t="n">
         <v>473374</v>
-      </c>
-      <c r="K251" t="n">
-        <v>2214206885</v>
       </c>
       <c r="L251" t="n">
         <v>-0.0006381620931716903</v>
@@ -22214,10 +22214,10 @@
         <v>3.2141336739038</v>
       </c>
       <c r="J252" t="n">
+        <v>20963</v>
+      </c>
+      <c r="K252" t="n">
         <v>1002990</v>
-      </c>
-      <c r="K252" t="n">
-        <v>4794292200</v>
       </c>
       <c r="L252" t="n">
         <v>0.03214133673903796</v>
@@ -22256,10 +22256,10 @@
         <v>-1.257991338420292</v>
       </c>
       <c r="J253" t="n">
+        <v>13900</v>
+      </c>
+      <c r="K253" t="n">
         <v>669408</v>
-      </c>
-      <c r="K253" t="n">
-        <v>3225542448</v>
       </c>
       <c r="L253" t="n">
         <v>-0.01257991338420295</v>
@@ -22298,10 +22298,10 @@
         <v>-1.106934001670846</v>
       </c>
       <c r="J254" t="n">
+        <v>10594</v>
+      </c>
+      <c r="K254" t="n">
         <v>502935</v>
-      </c>
-      <c r="K254" t="n">
-        <v>2391204457.5</v>
       </c>
       <c r="L254" t="n">
         <v>-0.01106934001670845</v>
@@ -22340,10 +22340,10 @@
         <v>-0.7602956705385415</v>
       </c>
       <c r="J255" t="n">
+        <v>10984</v>
+      </c>
+      <c r="K255" t="n">
         <v>518239</v>
-      </c>
-      <c r="K255" t="n">
-        <v>2446088080</v>
       </c>
       <c r="L255" t="n">
         <v>-0.007602956705385466</v>
@@ -22382,10 +22382,10 @@
         <v>3.043200680995956</v>
       </c>
       <c r="J256" t="n">
+        <v>24860</v>
+      </c>
+      <c r="K256" t="n">
         <v>1185928</v>
-      </c>
-      <c r="K256" t="n">
-        <v>5678223264</v>
       </c>
       <c r="L256" t="n">
         <v>0.0304320068099595</v>
@@ -22424,10 +22424,10 @@
         <v>1.941346551011974</v>
       </c>
       <c r="J257" t="n">
+        <v>19400</v>
+      </c>
+      <c r="K257" t="n">
         <v>946321</v>
-      </c>
-      <c r="K257" t="n">
-        <v>4596044516.75</v>
       </c>
       <c r="L257" t="n">
         <v>0.01941346551011969</v>
@@ -22466,10 +22466,10 @@
         <v>-0.7698541329011397</v>
       </c>
       <c r="J258" t="n">
+        <v>21920</v>
+      </c>
+      <c r="K258" t="n">
         <v>1075827</v>
-      </c>
-      <c r="K258" t="n">
-        <v>5322116169</v>
       </c>
       <c r="L258" t="n">
         <v>-0.007698541329011377</v>
@@ -22508,10 +22508,10 @@
         <v>2.592895059207847</v>
       </c>
       <c r="J259" t="n">
+        <v>27387</v>
+      </c>
+      <c r="K259" t="n">
         <v>1358812</v>
-      </c>
-      <c r="K259" t="n">
-        <v>6777754256</v>
       </c>
       <c r="L259" t="n">
         <v>0.02592895059207856</v>
@@ -22550,10 +22550,10 @@
         <v>-0.4179104477611957</v>
       </c>
       <c r="J260" t="n">
+        <v>21049</v>
+      </c>
+      <c r="K260" t="n">
         <v>1051386</v>
-      </c>
-      <c r="K260" t="n">
-        <v>5240107824</v>
       </c>
       <c r="L260" t="n">
         <v>-0.004179104477611939</v>
@@ -22592,10 +22592,10 @@
         <v>-2.737809752198237</v>
       </c>
       <c r="J261" t="n">
+        <v>15124</v>
+      </c>
+      <c r="K261" t="n">
         <v>749617</v>
-      </c>
-      <c r="K261" t="n">
-        <v>3719599554</v>
       </c>
       <c r="L261" t="n">
         <v>-0.02737809752198239</v>
@@ -22634,10 +22634,10 @@
         <v>8.752825148962396</v>
       </c>
       <c r="J262" t="n">
+        <v>33894</v>
+      </c>
+      <c r="K262" t="n">
         <v>1727562</v>
-      </c>
-      <c r="K262" t="n">
-        <v>8796745704</v>
       </c>
       <c r="L262" t="n">
         <v>0.08752825148962406</v>
@@ -22676,10 +22676,10 @@
         <v>-1.681466087285095</v>
       </c>
       <c r="J263" t="n">
+        <v>21834</v>
+      </c>
+      <c r="K263" t="n">
         <v>1146413</v>
-      </c>
-      <c r="K263" t="n">
-        <v>6023253902</v>
       </c>
       <c r="L263" t="n">
         <v>-0.01681466087285099</v>
@@ -22718,10 +22718,10 @@
         <v>3.343581860107613</v>
       </c>
       <c r="J264" t="n">
+        <v>29781</v>
+      </c>
+      <c r="K264" t="n">
         <v>1569308</v>
-      </c>
-      <c r="K264" t="n">
-        <v>8226704863</v>
       </c>
       <c r="L264" t="n">
         <v>0.03343581860107614</v>
@@ -22760,10 +22760,10 @@
         <v>-0.5392339159538846</v>
       </c>
       <c r="J265" t="n">
+        <v>24611</v>
+      </c>
+      <c r="K265" t="n">
         <v>1320238</v>
-      </c>
-      <c r="K265" t="n">
-        <v>7123674188.5</v>
       </c>
       <c r="L265" t="n">
         <v>-0.00539233915953885</v>
@@ -22802,10 +22802,10 @@
         <v>1.794727986539542</v>
       </c>
       <c r="J266" t="n">
+        <v>20159</v>
+      </c>
+      <c r="K266" t="n">
         <v>1098671</v>
-      </c>
-      <c r="K266" t="n">
-        <v>5972100888.25</v>
       </c>
       <c r="L266" t="n">
         <v>0.01794727986539546</v>
